--- a/app/data/label_overrides.xlsx
+++ b/app/data/label_overrides.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
   <si>
     <t xml:space="preserve">table_id</t>
   </si>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">All International Mobility Program IMP permits Dec 31 year</t>
   </si>
   <si>
-    <t xml:space="preserve">All permits</t>
+    <t xml:space="preserve">All permits (at December 31)</t>
   </si>
   <si>
     <t xml:space="preserve">Canada – All International Mobility Program (IMP) work permit holders on December 31st by country of citizenship and year</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">International Mobility Program IMP permits Work Dec 31 year</t>
   </si>
   <si>
-    <t xml:space="preserve">Permits for work purposes only</t>
+    <t xml:space="preserve">Permits for work purposes only (at December 31)</t>
   </si>
   <si>
     <t xml:space="preserve">Canada – International Mobility Program (IMP) work permit holders (for work purposes only) on December 31st by country of citizenship and year</t>
@@ -248,9 +248,21 @@
     <t xml:space="preserve">International Mobility Program permits P/T program</t>
   </si>
   <si>
+    <t xml:space="preserve">Program Level 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canada - International Mobility Program work permit holders by province/territory of intended destination, program and year in which permit(s) became effective</t>
   </si>
   <si>
+    <t xml:space="preserve">Program Level 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program Level 4</t>
+  </si>
+  <si>
     <t xml:space="preserve">temporary_workers/66f66dec__canada_international_mobility_program_work_permit_holders_un</t>
   </si>
   <si>
@@ -281,30 +293,27 @@
     <t xml:space="preserve">International Mobility permits</t>
   </si>
   <si>
-    <t xml:space="preserve">All permits (at December 31)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Program</t>
-  </si>
-  <si>
     <t xml:space="preserve">Canada - International Mobility Program work permit holders by province/territory, program and year in which permit(s) became effective</t>
   </si>
   <si>
     <t xml:space="preserve">Year in which Permit(s) Became Effective</t>
   </si>
   <si>
+    <t xml:space="preserve">Category Level 4</t>
+  </si>
+  <si>
     <t xml:space="preserve">temporary_workers/8d4c4240__canada_international_mobility_program_work_permit_holders_wo</t>
   </si>
   <si>
     <t xml:space="preserve">International Mobility permits Work Dec 31</t>
   </si>
   <si>
-    <t xml:space="preserve">Permits for work purposes only (at December 31)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Canada - International Mobility Program work permit holders (work purpose only) on December 31st by province/territory and program</t>
   </si>
   <si>
+    <t xml:space="preserve">Category Level 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">temporary_workers/08d3441d__canada_work_permit_holders_for_humanitarian_compassionate_pu</t>
   </si>
   <si>
@@ -416,6 +425,9 @@
     <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Immigration Category</t>
   </si>
   <si>
+    <t xml:space="preserve">Category Level 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">permanent_residents/d839c522__canada_ex_qc_french_speaking_permanent_residents_by_province__pr_immcat</t>
   </si>
   <si>
@@ -536,16 +548,13 @@
     <t xml:space="preserve">Province of Claimant</t>
   </si>
   <si>
-    <t xml:space="preserve">Province of Residence at the Time of the Refugee Claim Decision</t>
+    <t xml:space="preserve">Outcome</t>
   </si>
   <si>
     <t xml:space="preserve">Open Dataset Request 833195 ENG - RPD decisions from 1997-2021 by outcome and province of claimant</t>
   </si>
   <si>
-    <t xml:space="preserve">Outcome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rpd_decisions/a7d8297c__refugee_protection_division_rpd_decisions</t>
+    <t xml:space="preserve">rpd_decisions/62f63e53__refugee_protection_division_rpd_decisions</t>
   </si>
   <si>
     <t xml:space="preserve">Refugee Protection Division RPD Decisions</t>
@@ -818,8 +827,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:H89" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H89"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:H113" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H113"/>
   <tableColumns count="8">
     <tableColumn id="1" name="table_id"/>
     <tableColumn id="2" name="Theme"/>
@@ -1764,13 +1773,13 @@
         <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
@@ -1778,25 +1787,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
         <v>54</v>
       </c>
       <c r="C26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s">
         <v>80</v>
-      </c>
-      <c r="D26" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" t="s">
-        <v>82</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
@@ -1804,25 +1813,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
         <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
@@ -1830,25 +1839,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B28" t="s">
         <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s">
         <v>13</v>
@@ -1868,13 +1877,13 @@
         <v>89</v>
       </c>
       <c r="E29" t="s">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
@@ -1882,25 +1891,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B30" t="s">
         <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="E30" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
@@ -1908,25 +1917,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
@@ -1934,25 +1943,25 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B32" t="s">
         <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
@@ -1960,25 +1969,25 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
       </c>
       <c r="C33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" t="s">
+        <v>79</v>
+      </c>
+      <c r="F33" t="s">
+        <v>79</v>
+      </c>
+      <c r="G33" t="s">
         <v>98</v>
-      </c>
-      <c r="D33" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" t="s">
-        <v>102</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
@@ -1986,77 +1995,77 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" t="s">
         <v>99</v>
       </c>
-      <c r="E34" t="s">
-        <v>13</v>
-      </c>
       <c r="F34" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H34" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="E35" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="F35" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="H35" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E36" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G36" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
@@ -2064,25 +2073,25 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E37" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G37" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
@@ -2090,25 +2099,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E38" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s">
         <v>105</v>
-      </c>
-      <c r="G38" t="s">
-        <v>117</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
@@ -2116,77 +2125,77 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" t="s">
+        <v>108</v>
+      </c>
+      <c r="G39" t="s">
         <v>109</v>
       </c>
-      <c r="C39" t="s">
+      <c r="H39" t="s">
         <v>110</v>
-      </c>
-      <c r="D39" t="s">
-        <v>111</v>
-      </c>
-      <c r="E39" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39" t="s">
-        <v>119</v>
-      </c>
-      <c r="H39" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E40" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="G40" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E41" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F41" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="G41" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
@@ -2194,25 +2203,25 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E42" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F42" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
@@ -2220,25 +2229,25 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="G43" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
@@ -2246,129 +2255,129 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E44" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="H44" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D45" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E45" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="G45" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="H45" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="D46" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="F46" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="G46" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="H46" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D47" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="E47" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="F47" t="s">
-        <v>12</v>
+        <v>115</v>
       </c>
       <c r="G47" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H47" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D48" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="F48" t="s">
         <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="H48" t="s">
         <v>13</v>
@@ -2376,51 +2385,51 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C49" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D49" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E49" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F49" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G49" t="s">
         <v>136</v>
       </c>
       <c r="H49" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="D50" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E50" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="F50" t="s">
         <v>13</v>
       </c>
       <c r="G50" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
@@ -2428,25 +2437,25 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C51" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="D51" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E51" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F51" t="s">
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="H51" t="s">
         <v>13</v>
@@ -2454,181 +2463,181 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="D52" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="G52" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="H52" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="D53" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E53" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F53" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="G53" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="H53" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C54" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E54" t="s">
         <v>13</v>
       </c>
       <c r="F54" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G54" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="H54" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C55" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="D55" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E55" t="s">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G55" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="H55" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C56" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="D56" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E56" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="F56" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="G56" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="H56" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C57" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="D57" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E57" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="H57" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="D58" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E58" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="F58" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="G58" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="H58" t="s">
         <v>13</v>
@@ -2636,25 +2645,25 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C59" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="D59" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E59" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="F59" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G59" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="H59" t="s">
         <v>13</v>
@@ -2662,25 +2671,25 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="B60" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="D60" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="E60" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="H60" t="s">
         <v>13</v>
@@ -2688,51 +2697,51 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="B61" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="C61" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="D61" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="E61" t="s">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="F61" t="s">
-        <v>176</v>
+        <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="H61" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="B62" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="C62" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="D62" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="F62" t="s">
-        <v>179</v>
+        <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
@@ -2740,103 +2749,103 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="B63" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="C63" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="D63" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>176</v>
+        <v>99</v>
       </c>
       <c r="F63" t="s">
-        <v>176</v>
+        <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="H63" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="B64" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="C64" t="s">
-        <v>182</v>
+        <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="E64" t="s">
-        <v>176</v>
+        <v>40</v>
       </c>
       <c r="F64" t="s">
-        <v>176</v>
+        <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="H64" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="B65" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C65" t="s">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="E65" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="G65" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="H65" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="B66" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C66" t="s">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="D66" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="E66" t="s">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="F66" t="s">
         <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="H66" t="s">
         <v>13</v>
@@ -2844,25 +2853,25 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="B67" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C67" t="s">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="D67" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="E67" t="s">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="F67" t="s">
         <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="H67" t="s">
         <v>13</v>
@@ -2870,51 +2879,51 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="B68" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C68" t="s">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="E68" t="s">
-        <v>193</v>
+        <v>13</v>
       </c>
       <c r="F68" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="G68" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="H68" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="B69" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C69" t="s">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="E69" t="s">
-        <v>196</v>
+        <v>148</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
       </c>
       <c r="G69" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="H69" t="s">
         <v>13</v>
@@ -2922,51 +2931,51 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="B70" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C70" t="s">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="D70" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="E70" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="F70" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="G70" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="H70" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="B71" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C71" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="D71" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="E71" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="F71" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G71" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="H71" t="s">
         <v>13</v>
@@ -2974,25 +2983,25 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="B72" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="D72" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="E72" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="F72" t="s">
         <v>13</v>
       </c>
       <c r="G72" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="H72" t="s">
         <v>13</v>
@@ -3000,25 +3009,25 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="B73" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C73" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="D73" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="E73" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="F73" t="s">
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="H73" t="s">
         <v>13</v>
@@ -3026,25 +3035,25 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="B74" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C74" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="D74" t="s">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="E74" t="s">
         <v>13</v>
       </c>
       <c r="F74" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G74" t="s">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="H74" t="s">
         <v>13</v>
@@ -3052,25 +3061,25 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="B75" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C75" t="s">
-        <v>209</v>
+        <v>112</v>
       </c>
       <c r="D75" t="s">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="E75" t="s">
-        <v>204</v>
+        <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G75" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="H75" t="s">
         <v>13</v>
@@ -3078,51 +3087,51 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="B76" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C76" t="s">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="D76" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="E76" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>178</v>
       </c>
       <c r="G76" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="H76" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="B77" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C77" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="D77" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="F77" t="s">
         <v>13</v>
       </c>
       <c r="G77" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="H77" t="s">
         <v>13</v>
@@ -3130,25 +3139,25 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="B78" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C78" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="D78" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="F78" t="s">
         <v>13</v>
       </c>
       <c r="G78" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="H78" t="s">
         <v>13</v>
@@ -3156,51 +3165,51 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="B79" t="s">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>221</v>
+        <v>185</v>
       </c>
       <c r="D79" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="E79" t="s">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>178</v>
       </c>
       <c r="G79" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="H79" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="B80" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="C80" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D80" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="E80" t="s">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="F80" t="s">
         <v>13</v>
       </c>
       <c r="G80" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="H80" t="s">
         <v>13</v>
@@ -3208,25 +3217,25 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="B81" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="C81" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="D81" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="E81" t="s">
-        <v>112</v>
+        <v>193</v>
       </c>
       <c r="F81" t="s">
         <v>13</v>
       </c>
       <c r="G81" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="H81" t="s">
         <v>13</v>
@@ -3234,25 +3243,25 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="B82" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="C82" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="D82" t="s">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="E82" t="s">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="F82" t="s">
         <v>13</v>
       </c>
       <c r="G82" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="H82" t="s">
         <v>13</v>
@@ -3260,25 +3269,25 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="B83" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="C83" t="s">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="D83" t="s">
-        <v>89</v>
+        <v>190</v>
       </c>
       <c r="E83" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
       <c r="F83" t="s">
         <v>13</v>
       </c>
       <c r="G83" t="s">
-        <v>239</v>
+        <v>195</v>
       </c>
       <c r="H83" t="s">
         <v>13</v>
@@ -3286,25 +3295,25 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="B84" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="C84" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="D84" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="E84" t="s">
-        <v>40</v>
+        <v>199</v>
       </c>
       <c r="F84" t="s">
         <v>13</v>
       </c>
       <c r="G84" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="H84" t="s">
         <v>13</v>
@@ -3312,25 +3321,25 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>243</v>
+        <v>197</v>
       </c>
       <c r="B85" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="C85" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="D85" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="E85" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="F85" t="s">
         <v>13</v>
       </c>
       <c r="G85" t="s">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="H85" t="s">
         <v>13</v>
@@ -3338,13 +3347,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>245</v>
+        <v>201</v>
       </c>
       <c r="B86" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="C86" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="D86" t="s">
         <v>68</v>
@@ -3356,7 +3365,7 @@
         <v>12</v>
       </c>
       <c r="G86" t="s">
-        <v>246</v>
+        <v>203</v>
       </c>
       <c r="H86" t="s">
         <v>13</v>
@@ -3364,25 +3373,25 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="B87" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="C87" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="D87" t="s">
         <v>68</v>
       </c>
       <c r="E87" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="F87" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="G87" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
       <c r="H87" t="s">
         <v>13</v>
@@ -3390,25 +3399,25 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
       <c r="B88" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="C88" t="s">
-        <v>248</v>
+        <v>202</v>
       </c>
       <c r="D88" t="s">
         <v>68</v>
       </c>
       <c r="E88" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="F88" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="G88" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="H88" t="s">
         <v>13</v>
@@ -3416,27 +3425,651 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
+        <v>209</v>
+      </c>
+      <c r="B89" t="s">
+        <v>188</v>
+      </c>
+      <c r="C89" t="s">
+        <v>202</v>
+      </c>
+      <c r="D89" t="s">
+        <v>56</v>
+      </c>
+      <c r="E89" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" t="s">
+        <v>108</v>
+      </c>
+      <c r="G89" t="s">
+        <v>210</v>
+      </c>
+      <c r="H89" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>211</v>
+      </c>
+      <c r="B90" t="s">
+        <v>188</v>
+      </c>
+      <c r="C90" t="s">
+        <v>212</v>
+      </c>
+      <c r="D90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E90" t="s">
+        <v>207</v>
+      </c>
+      <c r="F90" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" t="s">
+        <v>213</v>
+      </c>
+      <c r="H90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>214</v>
+      </c>
+      <c r="B91" t="s">
+        <v>188</v>
+      </c>
+      <c r="C91" t="s">
+        <v>215</v>
+      </c>
+      <c r="D91" t="s">
+        <v>56</v>
+      </c>
+      <c r="E91" t="s">
+        <v>40</v>
+      </c>
+      <c r="F91" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" t="s">
+        <v>216</v>
+      </c>
+      <c r="H91" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>217</v>
+      </c>
+      <c r="B92" t="s">
+        <v>188</v>
+      </c>
+      <c r="C92" t="s">
+        <v>215</v>
+      </c>
+      <c r="D92" t="s">
+        <v>56</v>
+      </c>
+      <c r="E92" t="s">
+        <v>207</v>
+      </c>
+      <c r="F92" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" t="s">
+        <v>218</v>
+      </c>
+      <c r="H92" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>219</v>
+      </c>
+      <c r="B93" t="s">
+        <v>188</v>
+      </c>
+      <c r="C93" t="s">
+        <v>220</v>
+      </c>
+      <c r="D93" t="s">
+        <v>56</v>
+      </c>
+      <c r="E93" t="s">
+        <v>40</v>
+      </c>
+      <c r="F93" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" t="s">
+        <v>221</v>
+      </c>
+      <c r="H93" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>222</v>
+      </c>
+      <c r="B94" t="s">
+        <v>223</v>
+      </c>
+      <c r="C94" t="s">
+        <v>224</v>
+      </c>
+      <c r="D94" t="s">
+        <v>225</v>
+      </c>
+      <c r="E94" t="s">
+        <v>115</v>
+      </c>
+      <c r="F94" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" t="s">
+        <v>226</v>
+      </c>
+      <c r="H94" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>222</v>
+      </c>
+      <c r="B95" t="s">
+        <v>223</v>
+      </c>
+      <c r="C95" t="s">
+        <v>224</v>
+      </c>
+      <c r="D95" t="s">
+        <v>225</v>
+      </c>
+      <c r="E95" t="s">
+        <v>99</v>
+      </c>
+      <c r="F95" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" t="s">
+        <v>226</v>
+      </c>
+      <c r="H95" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>222</v>
+      </c>
+      <c r="B96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C96" t="s">
+        <v>224</v>
+      </c>
+      <c r="D96" t="s">
+        <v>225</v>
+      </c>
+      <c r="E96" t="s">
+        <v>95</v>
+      </c>
+      <c r="F96" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" t="s">
+        <v>226</v>
+      </c>
+      <c r="H96" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>227</v>
+      </c>
+      <c r="B97" t="s">
+        <v>223</v>
+      </c>
+      <c r="C97" t="s">
+        <v>228</v>
+      </c>
+      <c r="D97" t="s">
+        <v>229</v>
+      </c>
+      <c r="E97" t="s">
+        <v>115</v>
+      </c>
+      <c r="F97" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" t="s">
+        <v>230</v>
+      </c>
+      <c r="H97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>227</v>
+      </c>
+      <c r="B98" t="s">
+        <v>223</v>
+      </c>
+      <c r="C98" t="s">
+        <v>228</v>
+      </c>
+      <c r="D98" t="s">
+        <v>229</v>
+      </c>
+      <c r="E98" t="s">
+        <v>99</v>
+      </c>
+      <c r="F98" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" t="s">
+        <v>230</v>
+      </c>
+      <c r="H98" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>227</v>
+      </c>
+      <c r="B99" t="s">
+        <v>223</v>
+      </c>
+      <c r="C99" t="s">
+        <v>228</v>
+      </c>
+      <c r="D99" t="s">
+        <v>229</v>
+      </c>
+      <c r="E99" t="s">
+        <v>95</v>
+      </c>
+      <c r="F99" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" t="s">
+        <v>230</v>
+      </c>
+      <c r="H99" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>231</v>
+      </c>
+      <c r="B100" t="s">
+        <v>223</v>
+      </c>
+      <c r="C100" t="s">
+        <v>232</v>
+      </c>
+      <c r="D100" t="s">
+        <v>233</v>
+      </c>
+      <c r="E100" t="s">
+        <v>115</v>
+      </c>
+      <c r="F100" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" t="s">
+        <v>234</v>
+      </c>
+      <c r="H100" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>231</v>
+      </c>
+      <c r="B101" t="s">
+        <v>223</v>
+      </c>
+      <c r="C101" t="s">
+        <v>232</v>
+      </c>
+      <c r="D101" t="s">
+        <v>233</v>
+      </c>
+      <c r="E101" t="s">
+        <v>99</v>
+      </c>
+      <c r="F101" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" t="s">
+        <v>234</v>
+      </c>
+      <c r="H101" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>231</v>
+      </c>
+      <c r="B102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C102" t="s">
+        <v>232</v>
+      </c>
+      <c r="D102" t="s">
+        <v>233</v>
+      </c>
+      <c r="E102" t="s">
+        <v>95</v>
+      </c>
+      <c r="F102" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" t="s">
+        <v>234</v>
+      </c>
+      <c r="H102" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>235</v>
+      </c>
+      <c r="B103" t="s">
+        <v>223</v>
+      </c>
+      <c r="C103" t="s">
+        <v>236</v>
+      </c>
+      <c r="D103" t="s">
+        <v>237</v>
+      </c>
+      <c r="E103" t="s">
+        <v>115</v>
+      </c>
+      <c r="F103" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" t="s">
+        <v>238</v>
+      </c>
+      <c r="H103" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>235</v>
+      </c>
+      <c r="B104" t="s">
+        <v>223</v>
+      </c>
+      <c r="C104" t="s">
+        <v>236</v>
+      </c>
+      <c r="D104" t="s">
+        <v>237</v>
+      </c>
+      <c r="E104" t="s">
+        <v>99</v>
+      </c>
+      <c r="F104" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" t="s">
+        <v>238</v>
+      </c>
+      <c r="H104" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>235</v>
+      </c>
+      <c r="B105" t="s">
+        <v>223</v>
+      </c>
+      <c r="C105" t="s">
+        <v>236</v>
+      </c>
+      <c r="D105" t="s">
+        <v>237</v>
+      </c>
+      <c r="E105" t="s">
+        <v>95</v>
+      </c>
+      <c r="F105" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" t="s">
+        <v>238</v>
+      </c>
+      <c r="H105" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>239</v>
+      </c>
+      <c r="B106" t="s">
+        <v>240</v>
+      </c>
+      <c r="C106" t="s">
+        <v>241</v>
+      </c>
+      <c r="D106" t="s">
+        <v>56</v>
+      </c>
+      <c r="E106" t="s">
+        <v>40</v>
+      </c>
+      <c r="F106" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" t="s">
+        <v>242</v>
+      </c>
+      <c r="H106" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>243</v>
+      </c>
+      <c r="B107" t="s">
+        <v>240</v>
+      </c>
+      <c r="C107" t="s">
+        <v>244</v>
+      </c>
+      <c r="D107" t="s">
+        <v>68</v>
+      </c>
+      <c r="E107" t="s">
+        <v>40</v>
+      </c>
+      <c r="F107" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" t="s">
+        <v>245</v>
+      </c>
+      <c r="H107" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>246</v>
+      </c>
+      <c r="B108" t="s">
+        <v>240</v>
+      </c>
+      <c r="C108" t="s">
+        <v>244</v>
+      </c>
+      <c r="D108" t="s">
+        <v>68</v>
+      </c>
+      <c r="E108" t="s">
+        <v>69</v>
+      </c>
+      <c r="F108" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" t="s">
+        <v>247</v>
+      </c>
+      <c r="H108" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>248</v>
+      </c>
+      <c r="B109" t="s">
+        <v>240</v>
+      </c>
+      <c r="C109" t="s">
+        <v>244</v>
+      </c>
+      <c r="D109" t="s">
+        <v>68</v>
+      </c>
+      <c r="E109" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" t="s">
+        <v>249</v>
+      </c>
+      <c r="H109" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>248</v>
+      </c>
+      <c r="B110" t="s">
+        <v>240</v>
+      </c>
+      <c r="C110" t="s">
+        <v>244</v>
+      </c>
+      <c r="D110" t="s">
+        <v>68</v>
+      </c>
+      <c r="E110" t="s">
+        <v>75</v>
+      </c>
+      <c r="F110" t="s">
+        <v>75</v>
+      </c>
+      <c r="G110" t="s">
+        <v>249</v>
+      </c>
+      <c r="H110" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
         <v>250</v>
       </c>
-      <c r="B89" t="s">
-        <v>237</v>
-      </c>
-      <c r="C89" t="s">
+      <c r="B111" t="s">
+        <v>240</v>
+      </c>
+      <c r="C111" t="s">
         <v>251</v>
       </c>
-      <c r="D89" t="s">
-        <v>89</v>
-      </c>
-      <c r="E89" t="s">
-        <v>90</v>
-      </c>
-      <c r="F89" t="s">
-        <v>90</v>
-      </c>
-      <c r="G89" t="s">
+      <c r="D111" t="s">
+        <v>68</v>
+      </c>
+      <c r="E111" t="s">
+        <v>79</v>
+      </c>
+      <c r="F111" t="s">
+        <v>79</v>
+      </c>
+      <c r="G111" t="s">
         <v>252</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H111" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>253</v>
+      </c>
+      <c r="B112" t="s">
+        <v>240</v>
+      </c>
+      <c r="C112" t="s">
+        <v>254</v>
+      </c>
+      <c r="D112" t="s">
+        <v>56</v>
+      </c>
+      <c r="E112" t="s">
+        <v>79</v>
+      </c>
+      <c r="F112" t="s">
+        <v>79</v>
+      </c>
+      <c r="G112" t="s">
+        <v>255</v>
+      </c>
+      <c r="H112" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>253</v>
+      </c>
+      <c r="B113" t="s">
+        <v>240</v>
+      </c>
+      <c r="C113" t="s">
+        <v>254</v>
+      </c>
+      <c r="D113" t="s">
+        <v>56</v>
+      </c>
+      <c r="E113" t="s">
+        <v>99</v>
+      </c>
+      <c r="F113" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" t="s">
+        <v>255</v>
+      </c>
+      <c r="H113" t="s">
         <v>13</v>
       </c>
     </row>

--- a/app/data/label_overrides.xlsx
+++ b/app/data/label_overrides.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
   <si>
     <t xml:space="preserve">table_id</t>
   </si>
@@ -140,6 +140,12 @@
     <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship, Claim Office Type and Claim Year</t>
   </si>
   <si>
+    <t xml:space="preserve">Country Rank  Fr Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country of Citizenship  Fr Label</t>
+  </si>
+  <si>
     <t xml:space="preserve">asylum_claimants/0bb0bab1__canada_asylum_claimants_by_top_25_countries_of_citizenship_a</t>
   </si>
   <si>
@@ -263,6 +269,9 @@
     <t xml:space="preserve">Program Level 4</t>
   </si>
   <si>
+    <t xml:space="preserve">Program Level 5</t>
+  </si>
+  <si>
     <t xml:space="preserve">temporary_workers/66f66dec__canada_international_mobility_program_work_permit_holders_un</t>
   </si>
   <si>
@@ -302,6 +311,9 @@
     <t xml:space="preserve">Category Level 4</t>
   </si>
   <si>
+    <t xml:space="preserve">Category Level 5</t>
+  </si>
+  <si>
     <t xml:space="preserve">temporary_workers/8d4c4240__canada_international_mobility_program_work_permit_holders_wo</t>
   </si>
   <si>
@@ -381,6 +393,9 @@
   </si>
   <si>
     <t xml:space="preserve">Canada ex-QC - Admissions of French-Speaking Permanent Residents within Canada (excluding Quebec) by Province/Territory of Intended Destination and Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender  Fr Label</t>
   </si>
   <si>
     <t xml:space="preserve">permanent_residents/840a3387__canada_adoptions_via_permanent_residence_fc6_fc9_by_country_</t>
@@ -827,8 +842,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:H113" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H113"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:H122" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H122"/>
   <tableColumns count="8">
     <tableColumn id="1" name="table_id"/>
     <tableColumn id="2" name="Theme"/>
@@ -1475,25 +1490,25 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
@@ -1501,25 +1516,25 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H15" t="s">
         <v>13</v>
@@ -1527,25 +1542,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
         <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" t="s">
-        <v>49</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
@@ -1553,25 +1568,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
@@ -1579,16 +1594,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
         <v>40</v>
@@ -1597,7 +1612,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
@@ -1605,25 +1620,25 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H19" t="s">
         <v>13</v>
@@ -1631,25 +1646,25 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
@@ -1657,25 +1672,25 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
@@ -1683,16 +1698,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E22" t="s">
         <v>40</v>
@@ -1701,7 +1716,7 @@
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
@@ -1709,25 +1724,25 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
         <v>54</v>
-      </c>
-      <c r="C23" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" t="s">
-        <v>74</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
@@ -1735,25 +1750,25 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E24" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="F24" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
@@ -1761,25 +1776,25 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E25" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
@@ -1787,25 +1802,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
@@ -1813,25 +1828,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
@@ -1839,25 +1854,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H28" t="s">
         <v>13</v>
@@ -1865,25 +1880,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
@@ -1891,25 +1906,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
@@ -1917,25 +1932,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E31" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
@@ -1943,25 +1958,25 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E32" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
@@ -1969,25 +1984,25 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E33" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F33" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
@@ -1995,25 +2010,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E34" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
@@ -2021,25 +2036,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
@@ -2047,25 +2062,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
@@ -2073,25 +2088,25 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="F37" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
@@ -2099,25 +2114,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="F38" t="s">
         <v>13</v>
       </c>
       <c r="G38" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
@@ -2125,77 +2140,77 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="E39" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="F39" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="H39" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="D40" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="E40" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F40" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="G40" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="H40" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D41" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="E41" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
@@ -2203,25 +2218,25 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D42" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="E42" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="F42" t="s">
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
@@ -2229,25 +2244,25 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D43" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="F43" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="G43" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
@@ -2255,16 +2270,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E44" t="s">
         <v>12</v>
@@ -2273,7 +2288,7 @@
         <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="H44" t="s">
         <v>13</v>
@@ -2281,25 +2296,25 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="D45" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="E45" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G45" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
@@ -2307,25 +2322,25 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="B46" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="D46" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="E46" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="F46" t="s">
-        <v>127</v>
+        <v>13</v>
       </c>
       <c r="G46" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
@@ -2333,103 +2348,103 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" t="s">
+        <v>106</v>
+      </c>
+      <c r="E47" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" t="s">
         <v>112</v>
       </c>
-      <c r="C47" t="s">
-        <v>129</v>
-      </c>
-      <c r="D47" t="s">
-        <v>130</v>
-      </c>
-      <c r="E47" t="s">
-        <v>115</v>
-      </c>
-      <c r="F47" t="s">
-        <v>115</v>
-      </c>
       <c r="G47" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="H47" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" t="s">
+        <v>119</v>
+      </c>
+      <c r="F48" t="s">
+        <v>119</v>
+      </c>
+      <c r="G48" t="s">
+        <v>120</v>
+      </c>
+      <c r="H48" t="s">
         <v>114</v>
-      </c>
-      <c r="E48" t="s">
-        <v>40</v>
-      </c>
-      <c r="F48" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" t="s">
-        <v>134</v>
-      </c>
-      <c r="H48" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="B49" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D49" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E49" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F49" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="G49" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="H49" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C50" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E50" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F50" t="s">
         <v>13</v>
       </c>
       <c r="G50" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
@@ -2437,25 +2452,25 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B51" t="s">
+        <v>116</v>
+      </c>
+      <c r="C51" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" t="s">
         <v>112</v>
       </c>
-      <c r="C51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D51" t="s">
-        <v>114</v>
-      </c>
-      <c r="E51" t="s">
-        <v>99</v>
-      </c>
-      <c r="F51" t="s">
-        <v>13</v>
-      </c>
       <c r="G51" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H51" t="s">
         <v>13</v>
@@ -2463,51 +2478,51 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C52" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="D52" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E52" t="s">
-        <v>115</v>
+        <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>115</v>
+        <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="H52" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C53" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E53" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="F53" t="s">
         <v>13</v>
       </c>
       <c r="G53" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="H53" t="s">
         <v>13</v>
@@ -2515,77 +2530,77 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B54" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C54" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="D54" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="H54" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C55" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="D55" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="E55" t="s">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="F55" t="s">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="G55" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="H55" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D56" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="E56" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="F56" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="G56" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="H56" t="s">
         <v>13</v>
@@ -2593,77 +2608,77 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="B57" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D57" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E57" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="F57" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="G57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H57" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C58" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D58" t="s">
+        <v>118</v>
+      </c>
+      <c r="E58" t="s">
+        <v>119</v>
+      </c>
+      <c r="F58" t="s">
+        <v>119</v>
+      </c>
+      <c r="G58" t="s">
+        <v>141</v>
+      </c>
+      <c r="H58" t="s">
         <v>114</v>
-      </c>
-      <c r="E58" t="s">
-        <v>99</v>
-      </c>
-      <c r="F58" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" t="s">
-        <v>140</v>
-      </c>
-      <c r="H58" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C59" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D59" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E59" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="F59" t="s">
         <v>13</v>
       </c>
       <c r="G59" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H59" t="s">
         <v>13</v>
@@ -2671,25 +2686,25 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D60" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="H60" t="s">
         <v>13</v>
@@ -2697,51 +2712,51 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B61" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C61" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D61" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" t="s">
+        <v>119</v>
+      </c>
+      <c r="F61" t="s">
+        <v>119</v>
+      </c>
+      <c r="G61" t="s">
+        <v>145</v>
+      </c>
+      <c r="H61" t="s">
         <v>114</v>
-      </c>
-      <c r="E61" t="s">
-        <v>115</v>
-      </c>
-      <c r="F61" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" t="s">
-        <v>157</v>
-      </c>
-      <c r="H61" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B62" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C62" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D62" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E62" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="F62" t="s">
         <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
@@ -2749,129 +2764,129 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B63" t="s">
+        <v>116</v>
+      </c>
+      <c r="C63" t="s">
+        <v>147</v>
+      </c>
+      <c r="D63" t="s">
+        <v>118</v>
+      </c>
+      <c r="E63" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" t="s">
         <v>112</v>
       </c>
-      <c r="C63" t="s">
-        <v>156</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="G63" t="s">
+        <v>148</v>
+      </c>
+      <c r="H63" t="s">
         <v>114</v>
-      </c>
-      <c r="E63" t="s">
-        <v>99</v>
-      </c>
-      <c r="F63" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" t="s">
-        <v>157</v>
-      </c>
-      <c r="H63" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B64" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="D64" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G64" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="H64" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="D65" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="E65" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="G65" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H65" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B66" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C66" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="D66" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="E66" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="F66" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="G66" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="H66" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B67" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="D67" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="E67" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F67" t="s">
         <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="H67" t="s">
         <v>13</v>
@@ -2879,51 +2894,51 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B68" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="D68" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="E68" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="F68" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="G68" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="H68" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="D69" t="s">
+        <v>135</v>
+      </c>
+      <c r="E69" t="s">
+        <v>119</v>
+      </c>
+      <c r="F69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" t="s">
         <v>159</v>
-      </c>
-      <c r="E69" t="s">
-        <v>148</v>
-      </c>
-      <c r="F69" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" t="s">
-        <v>164</v>
       </c>
       <c r="H69" t="s">
         <v>13</v>
@@ -2931,51 +2946,51 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B70" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="D70" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="E70" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="G70" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H70" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="D71" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="E71" t="s">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="F71" t="s">
         <v>13</v>
       </c>
       <c r="G71" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H71" t="s">
         <v>13</v>
@@ -2983,25 +2998,25 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B72" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C72" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="D72" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="E72" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F72" t="s">
         <v>13</v>
       </c>
       <c r="G72" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H72" t="s">
         <v>13</v>
@@ -3009,25 +3024,25 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B73" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D73" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E73" t="s">
-        <v>168</v>
+        <v>40</v>
       </c>
       <c r="F73" t="s">
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H73" t="s">
         <v>13</v>
@@ -3035,51 +3050,51 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B74" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D74" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E74" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="F74" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="G74" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H74" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B75" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D75" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E75" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="F75" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G75" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="H75" t="s">
         <v>13</v>
@@ -3087,77 +3102,77 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B76" t="s">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="C76" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="D76" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="E76" t="s">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="F76" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
       <c r="G76" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="H76" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="B77" t="s">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="C77" t="s">
-        <v>181</v>
+        <v>116</v>
       </c>
       <c r="D77" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="E77" t="s">
-        <v>182</v>
+        <v>13</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="G77" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="H77" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="C78" t="s">
-        <v>181</v>
+        <v>116</v>
       </c>
       <c r="D78" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="E78" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="F78" t="s">
         <v>13</v>
       </c>
       <c r="G78" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="H78" t="s">
         <v>13</v>
@@ -3165,51 +3180,51 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B79" t="s">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="C79" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="D79" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="E79" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="F79" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="G79" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="H79" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="B80" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="C80" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="D80" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>191</v>
+        <v>103</v>
       </c>
       <c r="F80" t="s">
         <v>13</v>
       </c>
       <c r="G80" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="H80" t="s">
         <v>13</v>
@@ -3217,25 +3232,25 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="B81" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="C81" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="D81" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="E81" t="s">
-        <v>193</v>
+        <v>98</v>
       </c>
       <c r="F81" t="s">
         <v>13</v>
       </c>
       <c r="G81" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="H81" t="s">
         <v>13</v>
@@ -3243,25 +3258,25 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="B82" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="C82" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="D82" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="E82" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="F82" t="s">
         <v>13</v>
       </c>
       <c r="G82" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="H82" t="s">
         <v>13</v>
@@ -3269,25 +3284,25 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="C83" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="D83" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="E83" t="s">
-        <v>196</v>
+        <v>13</v>
       </c>
       <c r="F83" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="G83" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="H83" t="s">
         <v>13</v>
@@ -3295,25 +3310,25 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="B84" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="C84" t="s">
-        <v>198</v>
+        <v>116</v>
       </c>
       <c r="D84" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="E84" t="s">
-        <v>199</v>
+        <v>12</v>
       </c>
       <c r="F84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G84" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="H84" t="s">
         <v>13</v>
@@ -3321,51 +3336,51 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B85" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C85" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="D85" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E85" t="s">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>183</v>
       </c>
       <c r="G85" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="H85" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="B86" t="s">
+        <v>180</v>
+      </c>
+      <c r="C86" t="s">
+        <v>186</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>187</v>
+      </c>
+      <c r="F86" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" t="s">
         <v>188</v>
-      </c>
-      <c r="C86" t="s">
-        <v>202</v>
-      </c>
-      <c r="D86" t="s">
-        <v>68</v>
-      </c>
-      <c r="E86" t="s">
-        <v>12</v>
-      </c>
-      <c r="F86" t="s">
-        <v>12</v>
-      </c>
-      <c r="G86" t="s">
-        <v>203</v>
       </c>
       <c r="H86" t="s">
         <v>13</v>
@@ -3373,25 +3388,25 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="B87" t="s">
+        <v>180</v>
+      </c>
+      <c r="C87" t="s">
+        <v>186</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>183</v>
+      </c>
+      <c r="F87" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" t="s">
         <v>188</v>
-      </c>
-      <c r="C87" t="s">
-        <v>202</v>
-      </c>
-      <c r="D87" t="s">
-        <v>68</v>
-      </c>
-      <c r="E87" t="s">
-        <v>40</v>
-      </c>
-      <c r="F87" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" t="s">
-        <v>205</v>
       </c>
       <c r="H87" t="s">
         <v>13</v>
@@ -3399,51 +3414,51 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C88" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D88" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="E88" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="F88" t="s">
-        <v>13</v>
+        <v>183</v>
       </c>
       <c r="G88" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="H88" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="B89" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C89" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>195</v>
       </c>
       <c r="E89" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="F89" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="G89" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="H89" t="s">
         <v>13</v>
@@ -3451,25 +3466,25 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B90" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C90" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>195</v>
       </c>
       <c r="E90" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="F90" t="s">
         <v>13</v>
       </c>
       <c r="G90" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="H90" t="s">
         <v>13</v>
@@ -3477,25 +3492,25 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="B91" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C91" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>195</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
       <c r="F91" t="s">
         <v>13</v>
       </c>
       <c r="G91" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="H91" t="s">
         <v>13</v>
@@ -3503,25 +3518,25 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B92" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C92" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="D92" t="s">
-        <v>56</v>
+        <v>195</v>
       </c>
       <c r="E92" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F92" t="s">
         <v>13</v>
       </c>
       <c r="G92" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="H92" t="s">
         <v>13</v>
@@ -3529,25 +3544,25 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="B93" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C93" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>195</v>
       </c>
       <c r="E93" t="s">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="F93" t="s">
         <v>13</v>
       </c>
       <c r="G93" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="H93" t="s">
         <v>13</v>
@@ -3555,25 +3570,25 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="B94" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="C94" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="D94" t="s">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="E94" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F94" t="s">
         <v>13</v>
       </c>
       <c r="G94" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="H94" t="s">
         <v>13</v>
@@ -3581,25 +3596,25 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="B95" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="C95" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D95" t="s">
-        <v>225</v>
+        <v>70</v>
       </c>
       <c r="E95" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="F95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G95" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="H95" t="s">
         <v>13</v>
@@ -3607,25 +3622,25 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B96" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="C96" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D96" t="s">
-        <v>225</v>
+        <v>70</v>
       </c>
       <c r="E96" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="F96" t="s">
         <v>13</v>
       </c>
       <c r="G96" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="H96" t="s">
         <v>13</v>
@@ -3633,25 +3648,25 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="B97" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="C97" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="D97" t="s">
-        <v>229</v>
+        <v>70</v>
       </c>
       <c r="E97" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="F97" t="s">
         <v>13</v>
       </c>
       <c r="G97" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="H97" t="s">
         <v>13</v>
@@ -3659,25 +3674,25 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="B98" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="C98" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="D98" t="s">
-        <v>229</v>
+        <v>58</v>
       </c>
       <c r="E98" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="G98" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="H98" t="s">
         <v>13</v>
@@ -3685,25 +3700,25 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B99" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="C99" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D99" t="s">
-        <v>229</v>
+        <v>58</v>
       </c>
       <c r="E99" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="F99" t="s">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="H99" t="s">
         <v>13</v>
@@ -3711,25 +3726,25 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B100" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="C100" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D100" t="s">
-        <v>233</v>
+        <v>58</v>
       </c>
       <c r="E100" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
       </c>
       <c r="G100" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="H100" t="s">
         <v>13</v>
@@ -3737,25 +3752,25 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B101" t="s">
+        <v>193</v>
+      </c>
+      <c r="C101" t="s">
+        <v>220</v>
+      </c>
+      <c r="D101" t="s">
+        <v>58</v>
+      </c>
+      <c r="E101" t="s">
+        <v>212</v>
+      </c>
+      <c r="F101" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" t="s">
         <v>223</v>
-      </c>
-      <c r="C101" t="s">
-        <v>232</v>
-      </c>
-      <c r="D101" t="s">
-        <v>233</v>
-      </c>
-      <c r="E101" t="s">
-        <v>99</v>
-      </c>
-      <c r="F101" t="s">
-        <v>13</v>
-      </c>
-      <c r="G101" t="s">
-        <v>234</v>
       </c>
       <c r="H101" t="s">
         <v>13</v>
@@ -3763,25 +3778,25 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B102" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="C102" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D102" t="s">
-        <v>233</v>
+        <v>58</v>
       </c>
       <c r="E102" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="F102" t="s">
         <v>13</v>
       </c>
       <c r="G102" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="H102" t="s">
         <v>13</v>
@@ -3789,25 +3804,25 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B103" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C103" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D103" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E103" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F103" t="s">
         <v>13</v>
       </c>
       <c r="G103" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="H103" t="s">
         <v>13</v>
@@ -3815,25 +3830,25 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B104" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C104" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D104" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E104" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F104" t="s">
         <v>13</v>
       </c>
       <c r="G104" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="H104" t="s">
         <v>13</v>
@@ -3841,25 +3856,25 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B105" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C105" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D105" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E105" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F105" t="s">
         <v>13</v>
       </c>
       <c r="G105" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="H105" t="s">
         <v>13</v>
@@ -3867,25 +3882,25 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B106" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C106" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D106" t="s">
-        <v>56</v>
+        <v>234</v>
       </c>
       <c r="E106" t="s">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="F106" t="s">
         <v>13</v>
       </c>
       <c r="G106" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H106" t="s">
         <v>13</v>
@@ -3893,25 +3908,25 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B107" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C107" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D107" t="s">
-        <v>68</v>
+        <v>234</v>
       </c>
       <c r="E107" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="F107" t="s">
         <v>13</v>
       </c>
       <c r="G107" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H107" t="s">
         <v>13</v>
@@ -3919,25 +3934,25 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B108" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C108" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D108" t="s">
-        <v>68</v>
+        <v>234</v>
       </c>
       <c r="E108" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="F108" t="s">
         <v>13</v>
       </c>
       <c r="G108" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="H108" t="s">
         <v>13</v>
@@ -3945,25 +3960,25 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B109" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C109" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D109" t="s">
-        <v>68</v>
+        <v>238</v>
       </c>
       <c r="E109" t="s">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="F109" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G109" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="H109" t="s">
         <v>13</v>
@@ -3971,25 +3986,25 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B110" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C110" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D110" t="s">
-        <v>68</v>
+        <v>238</v>
       </c>
       <c r="E110" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="F110" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="G110" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="H110" t="s">
         <v>13</v>
@@ -3997,25 +4012,25 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="B111" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C111" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D111" t="s">
-        <v>68</v>
+        <v>238</v>
       </c>
       <c r="E111" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="F111" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="G111" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="H111" t="s">
         <v>13</v>
@@ -4023,25 +4038,25 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="B112" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C112" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="D112" t="s">
-        <v>56</v>
+        <v>242</v>
       </c>
       <c r="E112" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="F112" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="G112" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="H112" t="s">
         <v>13</v>
@@ -4049,27 +4064,261 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
+        <v>240</v>
+      </c>
+      <c r="B113" t="s">
+        <v>228</v>
+      </c>
+      <c r="C113" t="s">
+        <v>241</v>
+      </c>
+      <c r="D113" t="s">
+        <v>242</v>
+      </c>
+      <c r="E113" t="s">
+        <v>103</v>
+      </c>
+      <c r="F113" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" t="s">
+        <v>243</v>
+      </c>
+      <c r="H113" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>240</v>
+      </c>
+      <c r="B114" t="s">
+        <v>228</v>
+      </c>
+      <c r="C114" t="s">
+        <v>241</v>
+      </c>
+      <c r="D114" t="s">
+        <v>242</v>
+      </c>
+      <c r="E114" t="s">
+        <v>98</v>
+      </c>
+      <c r="F114" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" t="s">
+        <v>243</v>
+      </c>
+      <c r="H114" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>244</v>
+      </c>
+      <c r="B115" t="s">
+        <v>245</v>
+      </c>
+      <c r="C115" t="s">
+        <v>246</v>
+      </c>
+      <c r="D115" t="s">
+        <v>58</v>
+      </c>
+      <c r="E115" t="s">
+        <v>40</v>
+      </c>
+      <c r="F115" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" t="s">
+        <v>247</v>
+      </c>
+      <c r="H115" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>248</v>
+      </c>
+      <c r="B116" t="s">
+        <v>245</v>
+      </c>
+      <c r="C116" t="s">
+        <v>249</v>
+      </c>
+      <c r="D116" t="s">
+        <v>70</v>
+      </c>
+      <c r="E116" t="s">
+        <v>40</v>
+      </c>
+      <c r="F116" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" t="s">
+        <v>250</v>
+      </c>
+      <c r="H116" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>251</v>
+      </c>
+      <c r="B117" t="s">
+        <v>245</v>
+      </c>
+      <c r="C117" t="s">
+        <v>249</v>
+      </c>
+      <c r="D117" t="s">
+        <v>70</v>
+      </c>
+      <c r="E117" t="s">
+        <v>71</v>
+      </c>
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" t="s">
+        <v>252</v>
+      </c>
+      <c r="H117" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
         <v>253</v>
       </c>
-      <c r="B113" t="s">
-        <v>240</v>
-      </c>
-      <c r="C113" t="s">
+      <c r="B118" t="s">
+        <v>245</v>
+      </c>
+      <c r="C118" t="s">
+        <v>249</v>
+      </c>
+      <c r="D118" t="s">
+        <v>70</v>
+      </c>
+      <c r="E118" t="s">
+        <v>12</v>
+      </c>
+      <c r="F118" t="s">
+        <v>12</v>
+      </c>
+      <c r="G118" t="s">
         <v>254</v>
       </c>
-      <c r="D113" t="s">
-        <v>56</v>
-      </c>
-      <c r="E113" t="s">
-        <v>99</v>
-      </c>
-      <c r="F113" t="s">
-        <v>13</v>
-      </c>
-      <c r="G113" t="s">
+      <c r="H118" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>253</v>
+      </c>
+      <c r="B119" t="s">
+        <v>245</v>
+      </c>
+      <c r="C119" t="s">
+        <v>249</v>
+      </c>
+      <c r="D119" t="s">
+        <v>70</v>
+      </c>
+      <c r="E119" t="s">
+        <v>77</v>
+      </c>
+      <c r="F119" t="s">
+        <v>77</v>
+      </c>
+      <c r="G119" t="s">
+        <v>254</v>
+      </c>
+      <c r="H119" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
         <v>255</v>
       </c>
-      <c r="H113" t="s">
+      <c r="B120" t="s">
+        <v>245</v>
+      </c>
+      <c r="C120" t="s">
+        <v>256</v>
+      </c>
+      <c r="D120" t="s">
+        <v>70</v>
+      </c>
+      <c r="E120" t="s">
+        <v>81</v>
+      </c>
+      <c r="F120" t="s">
+        <v>81</v>
+      </c>
+      <c r="G120" t="s">
+        <v>257</v>
+      </c>
+      <c r="H120" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>258</v>
+      </c>
+      <c r="B121" t="s">
+        <v>245</v>
+      </c>
+      <c r="C121" t="s">
+        <v>259</v>
+      </c>
+      <c r="D121" t="s">
+        <v>58</v>
+      </c>
+      <c r="E121" t="s">
+        <v>81</v>
+      </c>
+      <c r="F121" t="s">
+        <v>81</v>
+      </c>
+      <c r="G121" t="s">
+        <v>260</v>
+      </c>
+      <c r="H121" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>258</v>
+      </c>
+      <c r="B122" t="s">
+        <v>245</v>
+      </c>
+      <c r="C122" t="s">
+        <v>259</v>
+      </c>
+      <c r="D122" t="s">
+        <v>58</v>
+      </c>
+      <c r="E122" t="s">
+        <v>103</v>
+      </c>
+      <c r="F122" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" t="s">
+        <v>260</v>
+      </c>
+      <c r="H122" t="s">
         <v>13</v>
       </c>
     </row>

--- a/app/data/label_overrides.xlsx
+++ b/app/data/label_overrides.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
   <si>
     <t xml:space="preserve">table_id</t>
   </si>
@@ -140,12 +140,6 @@
     <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship, Claim Office Type and Claim Year</t>
   </si>
   <si>
-    <t xml:space="preserve">Country Rank  Fr Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country of Citizenship  Fr Label</t>
-  </si>
-  <si>
     <t xml:space="preserve">asylum_claimants/0bb0bab1__canada_asylum_claimants_by_top_25_countries_of_citizenship_a</t>
   </si>
   <si>
@@ -395,9 +389,6 @@
     <t xml:space="preserve">Canada ex-QC - Admissions of French-Speaking Permanent Residents within Canada (excluding Quebec) by Province/Territory of Intended Destination and Gender</t>
   </si>
   <si>
-    <t xml:space="preserve">Gender  Fr Label</t>
-  </si>
-  <si>
     <t xml:space="preserve">permanent_residents/840a3387__canada_adoptions_via_permanent_residence_fc6_fc9_by_country_</t>
   </si>
   <si>
@@ -605,21 +596,21 @@
     <t xml:space="preserve">DLI Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Public/Private</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canada - Post-Secondary by P/T of Designated Learning Institution, DLI name, Public/Private and Year in which permit(s) became effective</t>
   </si>
   <si>
-    <t xml:space="preserve">Public/Private</t>
-  </si>
-  <si>
     <t xml:space="preserve">study_permit_holders/f49cfb41__canada_post_secondary_by_p_t_of_designated_learning_institut</t>
   </si>
   <si>
+    <t xml:space="preserve">Institution Type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canada - Post-Secondary by P/T of Designated Learning Institution, DLI name, Institution Type and Year in which permit(s) became effective</t>
   </si>
   <si>
-    <t xml:space="preserve">Institution Type</t>
-  </si>
-  <si>
     <t xml:space="preserve">study_permit_holders/77b26dc4__canada_post_secondary_by_p_t_of_designated_learning_institut</t>
   </si>
   <si>
@@ -627,6 +618,9 @@
   </si>
   <si>
     <t xml:space="preserve">Citizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Institution Type and Citizenship</t>
   </si>
   <si>
     <t xml:space="preserve">Canada - Post-Secondary by P/T of Designated Learning Institution Type, Citizenship and Year in which permit(s) became effective</t>
@@ -842,8 +836,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:H122" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H122"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:H115" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H115"/>
   <tableColumns count="8">
     <tableColumn id="1" name="table_id"/>
     <tableColumn id="2" name="Theme"/>
@@ -1490,25 +1484,25 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
@@ -1516,25 +1510,25 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H15" t="s">
         <v>13</v>
@@ -1542,25 +1536,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
@@ -1568,25 +1562,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
@@ -1594,16 +1588,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>40</v>
@@ -1612,7 +1606,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
@@ -1620,25 +1614,25 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H19" t="s">
         <v>13</v>
@@ -1646,25 +1640,25 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
@@ -1672,25 +1666,25 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
@@ -1698,16 +1692,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
         <v>40</v>
@@ -1716,7 +1710,7 @@
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
@@ -1724,25 +1718,25 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
@@ -1750,25 +1744,25 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
@@ -1776,25 +1770,25 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
@@ -1802,25 +1796,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
@@ -1828,25 +1822,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" t="s">
         <v>68</v>
       </c>
-      <c r="B27" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" t="s">
-        <v>70</v>
-      </c>
       <c r="E27" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
@@ -1854,25 +1848,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s">
         <v>13</v>
@@ -1880,25 +1874,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
@@ -1906,25 +1900,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E30" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="F30" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
@@ -1932,25 +1926,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" t="s">
         <v>79</v>
       </c>
-      <c r="D31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E31" t="s">
-        <v>80</v>
-      </c>
       <c r="F31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
@@ -1958,25 +1952,25 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
@@ -1984,25 +1978,25 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E33" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
@@ -2010,25 +2004,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
@@ -2036,25 +2030,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
@@ -2062,25 +2056,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
@@ -2088,25 +2082,25 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F37" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
@@ -2114,25 +2108,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G38" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
@@ -2140,25 +2134,25 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="E39" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G39" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H39" t="s">
         <v>13</v>
@@ -2166,25 +2160,25 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="E40" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="F40" t="s">
         <v>13</v>
       </c>
       <c r="G40" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
@@ -2192,77 +2186,77 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="E41" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="G41" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="E42" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="G42" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="H42" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="E43" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="F43" t="s">
         <v>13</v>
       </c>
       <c r="G43" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
@@ -2270,25 +2264,25 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D44" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E44" t="s">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G44" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H44" t="s">
         <v>13</v>
@@ -2296,25 +2290,25 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="C45" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F45" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="G45" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
@@ -2322,25 +2316,25 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
@@ -2348,77 +2342,77 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="C47" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D47" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="E47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="G47" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="H47" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D48" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E48" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F48" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G48" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H48" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="B49" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C49" t="s">
+        <v>131</v>
+      </c>
+      <c r="D49" t="s">
+        <v>132</v>
+      </c>
+      <c r="E49" t="s">
         <v>117</v>
       </c>
-      <c r="D49" t="s">
-        <v>118</v>
-      </c>
-      <c r="E49" t="s">
-        <v>121</v>
-      </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="G49" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H49" t="s">
         <v>13</v>
@@ -2426,25 +2420,25 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B50" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" t="s">
         <v>116</v>
       </c>
-      <c r="C50" t="s">
-        <v>117</v>
-      </c>
-      <c r="D50" t="s">
-        <v>118</v>
-      </c>
       <c r="E50" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="F50" t="s">
         <v>13</v>
       </c>
       <c r="G50" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
@@ -2452,51 +2446,51 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="B51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" t="s">
+        <v>135</v>
+      </c>
+      <c r="D51" t="s">
         <v>116</v>
       </c>
-      <c r="C51" t="s">
+      <c r="E51" t="s">
         <v>117</v>
       </c>
-      <c r="D51" t="s">
-        <v>118</v>
-      </c>
-      <c r="E51" t="s">
-        <v>13</v>
-      </c>
       <c r="F51" t="s">
+        <v>117</v>
+      </c>
+      <c r="G51" t="s">
+        <v>138</v>
+      </c>
+      <c r="H51" t="s">
         <v>112</v>
-      </c>
-      <c r="G51" t="s">
-        <v>124</v>
-      </c>
-      <c r="H51" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B52" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" t="s">
+        <v>135</v>
+      </c>
+      <c r="D52" t="s">
         <v>116</v>
       </c>
-      <c r="C52" t="s">
-        <v>117</v>
-      </c>
-      <c r="D52" t="s">
-        <v>118</v>
-      </c>
       <c r="E52" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H52" t="s">
         <v>13</v>
@@ -2504,25 +2498,25 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" t="s">
+        <v>135</v>
+      </c>
+      <c r="D53" t="s">
         <v>116</v>
       </c>
-      <c r="C53" t="s">
-        <v>117</v>
-      </c>
-      <c r="D53" t="s">
-        <v>118</v>
-      </c>
       <c r="E53" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="F53" t="s">
         <v>13</v>
       </c>
       <c r="G53" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H53" t="s">
         <v>13</v>
@@ -2530,51 +2524,51 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B54" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" t="s">
+        <v>141</v>
+      </c>
+      <c r="D54" t="s">
         <v>116</v>
       </c>
-      <c r="C54" t="s">
-        <v>129</v>
-      </c>
-      <c r="D54" t="s">
-        <v>130</v>
-      </c>
       <c r="E54" t="s">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="F54" t="s">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="G54" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H54" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B55" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" t="s">
+        <v>141</v>
+      </c>
+      <c r="D55" t="s">
         <v>116</v>
       </c>
-      <c r="C55" t="s">
-        <v>129</v>
-      </c>
-      <c r="D55" t="s">
-        <v>130</v>
-      </c>
       <c r="E55" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="F55" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="G55" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H55" t="s">
         <v>13</v>
@@ -2582,129 +2576,129 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B56" t="s">
+        <v>114</v>
+      </c>
+      <c r="C56" t="s">
+        <v>144</v>
+      </c>
+      <c r="D56" t="s">
         <v>116</v>
       </c>
-      <c r="C56" t="s">
-        <v>134</v>
-      </c>
-      <c r="D56" t="s">
-        <v>135</v>
-      </c>
       <c r="E56" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="F56" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G56" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="H56" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B57" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" t="s">
+        <v>144</v>
+      </c>
+      <c r="D57" t="s">
         <v>116</v>
       </c>
-      <c r="C57" t="s">
-        <v>138</v>
-      </c>
-      <c r="D57" t="s">
-        <v>118</v>
-      </c>
       <c r="E57" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G57" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="H57" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B58" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" t="s">
+        <v>149</v>
+      </c>
+      <c r="D58" t="s">
         <v>116</v>
       </c>
-      <c r="C58" t="s">
-        <v>138</v>
-      </c>
-      <c r="D58" t="s">
-        <v>118</v>
-      </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="F58" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="G58" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="H58" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B59" t="s">
+        <v>114</v>
+      </c>
+      <c r="C59" t="s">
+        <v>153</v>
+      </c>
+      <c r="D59" t="s">
         <v>116</v>
       </c>
-      <c r="C59" t="s">
-        <v>138</v>
-      </c>
-      <c r="D59" t="s">
-        <v>118</v>
-      </c>
       <c r="E59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F59" t="s">
+        <v>117</v>
+      </c>
+      <c r="G59" t="s">
         <v>142</v>
       </c>
-      <c r="F59" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" t="s">
-        <v>141</v>
-      </c>
       <c r="H59" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" t="s">
+        <v>153</v>
+      </c>
+      <c r="D60" t="s">
         <v>116</v>
       </c>
-      <c r="C60" t="s">
-        <v>138</v>
-      </c>
-      <c r="D60" t="s">
-        <v>118</v>
-      </c>
       <c r="E60" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H60" t="s">
         <v>13</v>
@@ -2712,51 +2706,51 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B61" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" t="s">
+        <v>153</v>
+      </c>
+      <c r="D61" t="s">
         <v>116</v>
       </c>
-      <c r="C61" t="s">
-        <v>144</v>
-      </c>
-      <c r="D61" t="s">
-        <v>118</v>
-      </c>
       <c r="E61" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F61" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H61" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B62" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D62" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E62" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F62" t="s">
         <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
@@ -2764,77 +2758,77 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B63" t="s">
+        <v>114</v>
+      </c>
+      <c r="C63" t="s">
+        <v>158</v>
+      </c>
+      <c r="D63" t="s">
         <v>116</v>
       </c>
-      <c r="C63" t="s">
-        <v>147</v>
-      </c>
-      <c r="D63" t="s">
-        <v>118</v>
-      </c>
       <c r="E63" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="F63" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="H63" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B64" t="s">
+        <v>114</v>
+      </c>
+      <c r="C64" t="s">
+        <v>158</v>
+      </c>
+      <c r="D64" t="s">
         <v>116</v>
       </c>
-      <c r="C64" t="s">
-        <v>147</v>
-      </c>
-      <c r="D64" t="s">
-        <v>118</v>
-      </c>
       <c r="E64" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="F64" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="H64" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B65" t="s">
+        <v>114</v>
+      </c>
+      <c r="C65" t="s">
+        <v>158</v>
+      </c>
+      <c r="D65" t="s">
         <v>116</v>
       </c>
-      <c r="C65" t="s">
-        <v>152</v>
-      </c>
-      <c r="D65" t="s">
-        <v>118</v>
-      </c>
       <c r="E65" t="s">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="F65" t="s">
         <v>13</v>
       </c>
       <c r="G65" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H65" t="s">
         <v>13</v>
@@ -2842,77 +2836,77 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B66" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C66" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="D66" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="E66" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="F66" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="H66" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B67" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C67" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="E67" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="G67" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="H67" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B68" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C68" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="D68" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="E68" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F68" t="s">
         <v>13</v>
       </c>
       <c r="G68" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="H68" t="s">
         <v>13</v>
@@ -2920,25 +2914,25 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B69" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C69" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="D69" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="E69" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
       </c>
       <c r="G69" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H69" t="s">
         <v>13</v>
@@ -2946,51 +2940,51 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B70" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C70" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" t="s">
         <v>161</v>
       </c>
-      <c r="D70" t="s">
-        <v>118</v>
-      </c>
       <c r="E70" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="F70" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="G70" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H70" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C71" t="s">
+        <v>114</v>
+      </c>
+      <c r="D71" t="s">
         <v>161</v>
       </c>
-      <c r="D71" t="s">
-        <v>118</v>
-      </c>
       <c r="E71" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F71" t="s">
         <v>13</v>
       </c>
       <c r="G71" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H71" t="s">
         <v>13</v>
@@ -2998,51 +2992,51 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B72" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C72" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" t="s">
         <v>161</v>
       </c>
-      <c r="D72" t="s">
-        <v>118</v>
-      </c>
       <c r="E72" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F72" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="G72" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H72" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B73" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C73" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D73" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E73" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="F73" t="s">
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H73" t="s">
         <v>13</v>
@@ -3050,51 +3044,51 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B74" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C74" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D74" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E74" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F74" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="G74" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H74" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B75" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C75" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E75" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="F75" t="s">
         <v>13</v>
       </c>
       <c r="G75" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H75" t="s">
         <v>13</v>
@@ -3102,25 +3096,25 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B76" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C76" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D76" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E76" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="G76" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="H76" t="s">
         <v>13</v>
@@ -3128,103 +3122,103 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B77" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C77" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D77" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F77" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="G77" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H77" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B78" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="C78" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="D78" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E78" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="G78" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="H78" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B79" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="C79" t="s">
-        <v>116</v>
+        <v>183</v>
       </c>
       <c r="D79" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="E79" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="F79" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="G79" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="H79" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B80" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="C80" t="s">
-        <v>116</v>
+        <v>183</v>
       </c>
       <c r="D80" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>103</v>
+        <v>180</v>
       </c>
       <c r="F80" t="s">
         <v>13</v>
       </c>
       <c r="G80" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="H80" t="s">
         <v>13</v>
@@ -3232,51 +3226,51 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="B81" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="C81" t="s">
-        <v>116</v>
+        <v>187</v>
       </c>
       <c r="D81" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="E81" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="G81" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="H81" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="B82" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="C82" t="s">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="D82" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="E82" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F82" t="s">
-        <v>13</v>
+        <v>194</v>
       </c>
       <c r="G82" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="H82" t="s">
         <v>13</v>
@@ -3284,25 +3278,25 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B83" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="C83" t="s">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="D83" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="E83" t="s">
-        <v>13</v>
+        <v>194</v>
       </c>
       <c r="F83" t="s">
-        <v>112</v>
+        <v>193</v>
       </c>
       <c r="G83" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="H83" t="s">
         <v>13</v>
@@ -3310,25 +3304,25 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B84" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="C84" t="s">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="D84" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="E84" t="s">
-        <v>12</v>
+        <v>193</v>
       </c>
       <c r="F84" t="s">
-        <v>12</v>
+        <v>197</v>
       </c>
       <c r="G84" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="H84" t="s">
         <v>13</v>
@@ -3336,51 +3330,51 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C85" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D85" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="E85" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="F85" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G85" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="H85" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B86" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C86" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D86" t="s">
-        <v>13</v>
+        <v>192</v>
       </c>
       <c r="E86" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
+        <v>202</v>
       </c>
       <c r="G86" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="H86" t="s">
         <v>13</v>
@@ -3388,25 +3382,25 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B87" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C87" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D87" t="s">
-        <v>13</v>
+        <v>192</v>
       </c>
       <c r="E87" t="s">
-        <v>183</v>
+        <v>95</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="G87" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="H87" t="s">
         <v>13</v>
@@ -3414,51 +3408,51 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B88" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C88" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D88" t="s">
-        <v>183</v>
+        <v>68</v>
       </c>
       <c r="E88" t="s">
-        <v>183</v>
+        <v>12</v>
       </c>
       <c r="F88" t="s">
-        <v>183</v>
+        <v>12</v>
       </c>
       <c r="G88" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="H88" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B89" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C89" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D89" t="s">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="E89" t="s">
-        <v>196</v>
+        <v>40</v>
       </c>
       <c r="F89" t="s">
         <v>13</v>
       </c>
       <c r="G89" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="H89" t="s">
         <v>13</v>
@@ -3466,25 +3460,25 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="B90" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C90" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D90" t="s">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="E90" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="F90" t="s">
         <v>13</v>
       </c>
       <c r="G90" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="H90" t="s">
         <v>13</v>
@@ -3492,25 +3486,25 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B91" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C91" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D91" t="s">
-        <v>195</v>
+        <v>56</v>
       </c>
       <c r="E91" t="s">
-        <v>196</v>
+        <v>13</v>
       </c>
       <c r="F91" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="G91" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="H91" t="s">
         <v>13</v>
@@ -3518,25 +3512,25 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="B92" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C92" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="D92" t="s">
-        <v>195</v>
+        <v>56</v>
       </c>
       <c r="E92" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F92" t="s">
         <v>13</v>
       </c>
       <c r="G92" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="H92" t="s">
         <v>13</v>
@@ -3544,25 +3538,25 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="B93" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C93" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D93" t="s">
-        <v>195</v>
+        <v>56</v>
       </c>
       <c r="E93" t="s">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c r="F93" t="s">
         <v>13</v>
       </c>
       <c r="G93" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="H93" t="s">
         <v>13</v>
@@ -3570,25 +3564,25 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B94" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C94" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D94" t="s">
-        <v>195</v>
+        <v>56</v>
       </c>
       <c r="E94" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="F94" t="s">
         <v>13</v>
       </c>
       <c r="G94" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="H94" t="s">
         <v>13</v>
@@ -3596,25 +3590,25 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B95" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C95" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="D95" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E95" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F95" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G95" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="H95" t="s">
         <v>13</v>
@@ -3622,25 +3616,25 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="B96" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="C96" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="D96" t="s">
-        <v>70</v>
+        <v>228</v>
       </c>
       <c r="E96" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="F96" t="s">
         <v>13</v>
       </c>
       <c r="G96" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="H96" t="s">
         <v>13</v>
@@ -3648,25 +3642,25 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="B97" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="C97" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="D97" t="s">
-        <v>70</v>
+        <v>228</v>
       </c>
       <c r="E97" t="s">
-        <v>212</v>
+        <v>101</v>
       </c>
       <c r="F97" t="s">
         <v>13</v>
       </c>
       <c r="G97" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H97" t="s">
         <v>13</v>
@@ -3674,25 +3668,25 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B98" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="C98" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="D98" t="s">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="E98" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="F98" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="G98" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="H98" t="s">
         <v>13</v>
@@ -3700,25 +3694,25 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B99" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="C99" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="D99" t="s">
-        <v>58</v>
+        <v>232</v>
       </c>
       <c r="E99" t="s">
-        <v>212</v>
+        <v>117</v>
       </c>
       <c r="F99" t="s">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="H99" t="s">
         <v>13</v>
@@ -3726,25 +3720,25 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B100" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="C100" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D100" t="s">
-        <v>58</v>
+        <v>232</v>
       </c>
       <c r="E100" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
       </c>
       <c r="G100" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="H100" t="s">
         <v>13</v>
@@ -3752,25 +3746,25 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B101" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="C101" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D101" t="s">
-        <v>58</v>
+        <v>232</v>
       </c>
       <c r="E101" t="s">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="F101" t="s">
         <v>13</v>
       </c>
       <c r="G101" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="H101" t="s">
         <v>13</v>
@@ -3778,25 +3772,25 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B102" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="C102" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D102" t="s">
-        <v>58</v>
+        <v>236</v>
       </c>
       <c r="E102" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="F102" t="s">
         <v>13</v>
       </c>
       <c r="G102" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="H102" t="s">
         <v>13</v>
@@ -3804,25 +3798,25 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B103" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C103" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D103" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F103" t="s">
         <v>13</v>
       </c>
       <c r="G103" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="H103" t="s">
         <v>13</v>
@@ -3830,25 +3824,25 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B104" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C104" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D104" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F104" t="s">
         <v>13</v>
       </c>
       <c r="G104" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="H104" t="s">
         <v>13</v>
@@ -3856,25 +3850,25 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="B105" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C105" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D105" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E105" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="F105" t="s">
         <v>13</v>
       </c>
       <c r="G105" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="H105" t="s">
         <v>13</v>
@@ -3882,25 +3876,25 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B106" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C106" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D106" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E106" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F106" t="s">
         <v>13</v>
       </c>
       <c r="G106" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H106" t="s">
         <v>13</v>
@@ -3908,25 +3902,25 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B107" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C107" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D107" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E107" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F107" t="s">
         <v>13</v>
       </c>
       <c r="G107" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H107" t="s">
         <v>13</v>
@@ -3934,25 +3928,25 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B108" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C108" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D108" t="s">
-        <v>234</v>
+        <v>56</v>
       </c>
       <c r="E108" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="F108" t="s">
         <v>13</v>
       </c>
       <c r="G108" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="H108" t="s">
         <v>13</v>
@@ -3960,25 +3954,25 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B109" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C109" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D109" t="s">
-        <v>238</v>
+        <v>68</v>
       </c>
       <c r="E109" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="F109" t="s">
         <v>13</v>
       </c>
       <c r="G109" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H109" t="s">
         <v>13</v>
@@ -3986,25 +3980,25 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B110" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C110" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D110" t="s">
-        <v>238</v>
+        <v>68</v>
       </c>
       <c r="E110" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="F110" t="s">
         <v>13</v>
       </c>
       <c r="G110" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="H110" t="s">
         <v>13</v>
@@ -4012,25 +4006,25 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="B111" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C111" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D111" t="s">
-        <v>238</v>
+        <v>68</v>
       </c>
       <c r="E111" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="F111" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G111" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="H111" t="s">
         <v>13</v>
@@ -4038,25 +4032,25 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B112" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C112" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D112" t="s">
-        <v>242</v>
+        <v>68</v>
       </c>
       <c r="E112" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="F112" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="G112" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="H112" t="s">
         <v>13</v>
@@ -4064,25 +4058,25 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B113" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C113" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="D113" t="s">
-        <v>242</v>
+        <v>68</v>
       </c>
       <c r="E113" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="F113" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="G113" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="H113" t="s">
         <v>13</v>
@@ -4090,25 +4084,25 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B114" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C114" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="D114" t="s">
-        <v>242</v>
+        <v>56</v>
       </c>
       <c r="E114" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="F114" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="G114" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="H114" t="s">
         <v>13</v>
@@ -4116,209 +4110,27 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B115" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C115" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D115" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E115" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="F115" t="s">
         <v>13</v>
       </c>
       <c r="G115" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="H115" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>248</v>
-      </c>
-      <c r="B116" t="s">
-        <v>245</v>
-      </c>
-      <c r="C116" t="s">
-        <v>249</v>
-      </c>
-      <c r="D116" t="s">
-        <v>70</v>
-      </c>
-      <c r="E116" t="s">
-        <v>40</v>
-      </c>
-      <c r="F116" t="s">
-        <v>13</v>
-      </c>
-      <c r="G116" t="s">
-        <v>250</v>
-      </c>
-      <c r="H116" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>251</v>
-      </c>
-      <c r="B117" t="s">
-        <v>245</v>
-      </c>
-      <c r="C117" t="s">
-        <v>249</v>
-      </c>
-      <c r="D117" t="s">
-        <v>70</v>
-      </c>
-      <c r="E117" t="s">
-        <v>71</v>
-      </c>
-      <c r="F117" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" t="s">
-        <v>252</v>
-      </c>
-      <c r="H117" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>253</v>
-      </c>
-      <c r="B118" t="s">
-        <v>245</v>
-      </c>
-      <c r="C118" t="s">
-        <v>249</v>
-      </c>
-      <c r="D118" t="s">
-        <v>70</v>
-      </c>
-      <c r="E118" t="s">
-        <v>12</v>
-      </c>
-      <c r="F118" t="s">
-        <v>12</v>
-      </c>
-      <c r="G118" t="s">
-        <v>254</v>
-      </c>
-      <c r="H118" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>253</v>
-      </c>
-      <c r="B119" t="s">
-        <v>245</v>
-      </c>
-      <c r="C119" t="s">
-        <v>249</v>
-      </c>
-      <c r="D119" t="s">
-        <v>70</v>
-      </c>
-      <c r="E119" t="s">
-        <v>77</v>
-      </c>
-      <c r="F119" t="s">
-        <v>77</v>
-      </c>
-      <c r="G119" t="s">
-        <v>254</v>
-      </c>
-      <c r="H119" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>255</v>
-      </c>
-      <c r="B120" t="s">
-        <v>245</v>
-      </c>
-      <c r="C120" t="s">
-        <v>256</v>
-      </c>
-      <c r="D120" t="s">
-        <v>70</v>
-      </c>
-      <c r="E120" t="s">
-        <v>81</v>
-      </c>
-      <c r="F120" t="s">
-        <v>81</v>
-      </c>
-      <c r="G120" t="s">
-        <v>257</v>
-      </c>
-      <c r="H120" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>258</v>
-      </c>
-      <c r="B121" t="s">
-        <v>245</v>
-      </c>
-      <c r="C121" t="s">
-        <v>259</v>
-      </c>
-      <c r="D121" t="s">
-        <v>58</v>
-      </c>
-      <c r="E121" t="s">
-        <v>81</v>
-      </c>
-      <c r="F121" t="s">
-        <v>81</v>
-      </c>
-      <c r="G121" t="s">
-        <v>260</v>
-      </c>
-      <c r="H121" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>258</v>
-      </c>
-      <c r="B122" t="s">
-        <v>245</v>
-      </c>
-      <c r="C122" t="s">
-        <v>259</v>
-      </c>
-      <c r="D122" t="s">
-        <v>58</v>
-      </c>
-      <c r="E122" t="s">
-        <v>103</v>
-      </c>
-      <c r="F122" t="s">
-        <v>13</v>
-      </c>
-      <c r="G122" t="s">
-        <v>260</v>
-      </c>
-      <c r="H122" t="s">
         <v>13</v>
       </c>
     </row>

--- a/app/data/label_overrides.xlsx
+++ b/app/data/label_overrides.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
   <si>
     <t xml:space="preserve">table_id</t>
   </si>
@@ -428,10 +428,16 @@
     <t xml:space="preserve">permanent_residents/f72b7082__canada_ex_qc_french_speaking_permanent_residents_by_immigrat</t>
   </si>
   <si>
+    <t xml:space="preserve">Category Level 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immigration Category and Express Entry</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Immigration Category</t>
   </si>
   <si>
-    <t xml:space="preserve">Category Level 2</t>
+    <t xml:space="preserve">Express Entry</t>
   </si>
   <si>
     <t xml:space="preserve">permanent_residents/d839c522__canada_ex_qc_french_speaking_permanent_residents_by_province__pr_immcat</t>
@@ -836,8 +842,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:H115" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H115"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:H113" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H113"/>
   <tableColumns count="8">
     <tableColumn id="1" name="table_id"/>
     <tableColumn id="2" name="Theme"/>
@@ -2458,16 +2464,16 @@
         <v>116</v>
       </c>
       <c r="E51" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="F51" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="G51" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H51" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
@@ -2484,13 +2490,13 @@
         <v>116</v>
       </c>
       <c r="E52" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="G52" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H52" t="s">
         <v>13</v>
@@ -2498,103 +2504,103 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B53" t="s">
         <v>114</v>
       </c>
       <c r="C53" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D53" t="s">
         <v>116</v>
       </c>
       <c r="E53" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="G53" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H53" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B54" t="s">
         <v>114</v>
       </c>
       <c r="C54" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D54" t="s">
         <v>116</v>
       </c>
       <c r="E54" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="F54" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="G54" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H54" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B55" t="s">
         <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D55" t="s">
         <v>116</v>
       </c>
       <c r="E55" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="G55" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H55" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B56" t="s">
         <v>114</v>
       </c>
       <c r="C56" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D56" t="s">
         <v>116</v>
       </c>
       <c r="E56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H56" t="s">
         <v>112</v>
@@ -2602,103 +2608,103 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B57" t="s">
         <v>114</v>
       </c>
       <c r="C57" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D57" t="s">
         <v>116</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="F57" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G57" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H57" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B58" t="s">
         <v>114</v>
       </c>
       <c r="C58" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D58" t="s">
         <v>116</v>
       </c>
       <c r="E58" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="G58" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H58" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B59" t="s">
         <v>114</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D59" t="s">
         <v>116</v>
       </c>
       <c r="E59" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="F59" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="G59" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H59" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B60" t="s">
         <v>114</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
         <v>116</v>
       </c>
       <c r="E60" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H60" t="s">
         <v>13</v>
@@ -2706,25 +2712,25 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B61" t="s">
         <v>114</v>
       </c>
       <c r="C61" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D61" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="E61" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="F61" t="s">
         <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="H61" t="s">
         <v>13</v>
@@ -2732,25 +2738,25 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B62" t="s">
         <v>114</v>
       </c>
       <c r="C62" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D62" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E62" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="F62" t="s">
         <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
@@ -2758,25 +2764,25 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B63" t="s">
         <v>114</v>
       </c>
       <c r="C63" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D63" t="s">
         <v>116</v>
       </c>
       <c r="E63" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="F63" t="s">
         <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H63" t="s">
         <v>13</v>
@@ -2784,25 +2790,25 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B64" t="s">
         <v>114</v>
       </c>
       <c r="C64" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="D64" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="E64" t="s">
-        <v>139</v>
+        <v>40</v>
       </c>
       <c r="F64" t="s">
         <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H64" t="s">
         <v>13</v>
@@ -2810,33 +2816,33 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B65" t="s">
         <v>114</v>
       </c>
       <c r="C65" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="D65" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="E65" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="G65" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H65" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B66" t="s">
         <v>114</v>
@@ -2845,16 +2851,16 @@
         <v>114</v>
       </c>
       <c r="D66" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E66" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="F66" t="s">
         <v>13</v>
       </c>
       <c r="G66" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H66" t="s">
         <v>13</v>
@@ -2862,7 +2868,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B67" t="s">
         <v>114</v>
@@ -2871,24 +2877,24 @@
         <v>114</v>
       </c>
       <c r="D67" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E67" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="F67" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H67" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B68" t="s">
         <v>114</v>
@@ -2897,24 +2903,24 @@
         <v>114</v>
       </c>
       <c r="D68" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E68" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="F68" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="G68" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H68" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B69" t="s">
         <v>114</v>
@@ -2923,16 +2929,16 @@
         <v>114</v>
       </c>
       <c r="D69" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E69" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="F69" t="s">
         <v>13</v>
       </c>
       <c r="G69" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H69" t="s">
         <v>13</v>
@@ -2940,25 +2946,25 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>169</v>
+      </c>
+      <c r="B70" t="s">
+        <v>114</v>
+      </c>
+      <c r="C70" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" t="s">
         <v>163</v>
       </c>
-      <c r="B70" t="s">
-        <v>114</v>
-      </c>
-      <c r="C70" t="s">
-        <v>114</v>
-      </c>
-      <c r="D70" t="s">
-        <v>161</v>
-      </c>
       <c r="E70" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="F70" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G70" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H70" t="s">
         <v>112</v>
@@ -2966,7 +2972,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B71" t="s">
         <v>114</v>
@@ -2975,16 +2981,16 @@
         <v>114</v>
       </c>
       <c r="D71" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E71" t="s">
-        <v>150</v>
+        <v>101</v>
       </c>
       <c r="F71" t="s">
         <v>13</v>
       </c>
       <c r="G71" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H71" t="s">
         <v>13</v>
@@ -2992,7 +2998,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B72" t="s">
         <v>114</v>
@@ -3001,24 +3007,24 @@
         <v>114</v>
       </c>
       <c r="D72" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E72" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="F72" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="G72" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H72" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B73" t="s">
         <v>114</v>
@@ -3027,16 +3033,16 @@
         <v>114</v>
       </c>
       <c r="D73" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E73" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="F73" t="s">
         <v>13</v>
       </c>
       <c r="G73" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="H73" t="s">
         <v>13</v>
@@ -3044,7 +3050,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B74" t="s">
         <v>114</v>
@@ -3053,16 +3059,16 @@
         <v>114</v>
       </c>
       <c r="D74" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E74" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="G74" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H74" t="s">
         <v>13</v>
@@ -3070,7 +3076,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B75" t="s">
         <v>114</v>
@@ -3079,16 +3085,16 @@
         <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E75" t="s">
-        <v>170</v>
+        <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G75" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="H75" t="s">
         <v>13</v>
@@ -3096,51 +3102,51 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B76" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="C76" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="D76" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="E76" t="s">
-        <v>13</v>
+        <v>182</v>
       </c>
       <c r="F76" t="s">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="G76" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="H76" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B77" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="C77" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="D77" t="s">
-        <v>161</v>
+        <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>12</v>
+        <v>186</v>
       </c>
       <c r="F77" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G77" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H77" t="s">
         <v>13</v>
@@ -3148,77 +3154,77 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C78" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D78" t="s">
-        <v>179</v>
+        <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F78" t="s">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="G78" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H78" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>188</v>
+      </c>
+      <c r="B79" t="s">
+        <v>179</v>
+      </c>
+      <c r="C79" t="s">
+        <v>189</v>
+      </c>
+      <c r="D79" t="s">
         <v>182</v>
       </c>
-      <c r="B79" t="s">
-        <v>177</v>
-      </c>
-      <c r="C79" t="s">
-        <v>183</v>
-      </c>
-      <c r="D79" t="s">
-        <v>13</v>
-      </c>
       <c r="E79" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>182</v>
       </c>
       <c r="G79" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H79" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B80" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C80" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="D80" t="s">
-        <v>13</v>
+        <v>194</v>
       </c>
       <c r="E80" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F80" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="G80" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="H80" t="s">
         <v>13</v>
@@ -3226,51 +3232,51 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B81" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D81" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="E81" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="F81" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="G81" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="H81" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B82" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C82" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D82" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E82" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F82" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G82" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H82" t="s">
         <v>13</v>
@@ -3278,25 +3284,25 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B83" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C83" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D83" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E83" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G83" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H83" t="s">
         <v>13</v>
@@ -3304,25 +3310,25 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B84" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C84" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="D84" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E84" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="F84" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="G84" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H84" t="s">
         <v>13</v>
@@ -3330,25 +3336,25 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B85" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C85" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="D85" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E85" t="s">
-        <v>197</v>
+        <v>95</v>
       </c>
       <c r="F85" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G85" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H85" t="s">
         <v>13</v>
@@ -3356,25 +3362,25 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B86" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C86" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D86" t="s">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="E86" t="s">
-        <v>201</v>
+        <v>12</v>
       </c>
       <c r="F86" t="s">
-        <v>202</v>
+        <v>12</v>
       </c>
       <c r="G86" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H86" t="s">
         <v>13</v>
@@ -3382,25 +3388,25 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B87" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C87" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D87" t="s">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="E87" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="F87" t="s">
-        <v>201</v>
+        <v>13</v>
       </c>
       <c r="G87" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="H87" t="s">
         <v>13</v>
@@ -3408,25 +3414,25 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B88" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C88" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D88" t="s">
         <v>68</v>
       </c>
       <c r="E88" t="s">
-        <v>12</v>
+        <v>212</v>
       </c>
       <c r="F88" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G88" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="H88" t="s">
         <v>13</v>
@@ -3434,25 +3440,25 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
+        <v>214</v>
+      </c>
+      <c r="B89" t="s">
+        <v>192</v>
+      </c>
+      <c r="C89" t="s">
         <v>207</v>
       </c>
-      <c r="B89" t="s">
-        <v>190</v>
-      </c>
-      <c r="C89" t="s">
-        <v>205</v>
-      </c>
       <c r="D89" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E89" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="F89" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="G89" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="H89" t="s">
         <v>13</v>
@@ -3460,25 +3466,25 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B90" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C90" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="D90" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E90" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F90" t="s">
         <v>13</v>
       </c>
       <c r="G90" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H90" t="s">
         <v>13</v>
@@ -3486,25 +3492,25 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B91" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C91" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="D91" t="s">
         <v>56</v>
       </c>
       <c r="E91" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F91" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="G91" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H91" t="s">
         <v>13</v>
@@ -3512,25 +3518,25 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B92" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C92" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D92" t="s">
         <v>56</v>
       </c>
       <c r="E92" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F92" t="s">
         <v>13</v>
       </c>
       <c r="G92" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="H92" t="s">
         <v>13</v>
@@ -3538,13 +3544,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B93" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C93" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D93" t="s">
         <v>56</v>
@@ -3556,7 +3562,7 @@
         <v>13</v>
       </c>
       <c r="G93" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="H93" t="s">
         <v>13</v>
@@ -3564,25 +3570,25 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B94" t="s">
-        <v>190</v>
+        <v>228</v>
       </c>
       <c r="C94" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D94" t="s">
-        <v>56</v>
+        <v>230</v>
       </c>
       <c r="E94" t="s">
-        <v>210</v>
+        <v>117</v>
       </c>
       <c r="F94" t="s">
         <v>13</v>
       </c>
       <c r="G94" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="H94" t="s">
         <v>13</v>
@@ -3590,25 +3596,25 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B95" t="s">
-        <v>190</v>
+        <v>228</v>
       </c>
       <c r="C95" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D95" t="s">
-        <v>56</v>
+        <v>230</v>
       </c>
       <c r="E95" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="F95" t="s">
         <v>13</v>
       </c>
       <c r="G95" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="H95" t="s">
         <v>13</v>
@@ -3616,25 +3622,25 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B96" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C96" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D96" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E96" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="F96" t="s">
         <v>13</v>
       </c>
       <c r="G96" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H96" t="s">
         <v>13</v>
@@ -3642,25 +3648,25 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B97" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C97" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D97" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E97" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F97" t="s">
         <v>13</v>
       </c>
       <c r="G97" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="H97" t="s">
         <v>13</v>
@@ -3668,25 +3674,25 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B98" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C98" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D98" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E98" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F98" t="s">
         <v>13</v>
       </c>
       <c r="G98" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="H98" t="s">
         <v>13</v>
@@ -3694,25 +3700,25 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B99" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C99" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D99" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E99" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="F99" t="s">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H99" t="s">
         <v>13</v>
@@ -3720,25 +3726,25 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B100" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C100" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D100" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E100" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
       </c>
       <c r="G100" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="H100" t="s">
         <v>13</v>
@@ -3746,25 +3752,25 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B101" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C101" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D101" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E101" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F101" t="s">
         <v>13</v>
       </c>
       <c r="G101" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="H101" t="s">
         <v>13</v>
@@ -3772,25 +3778,25 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B102" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C102" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E102" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="F102" t="s">
         <v>13</v>
       </c>
       <c r="G102" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H102" t="s">
         <v>13</v>
@@ -3798,25 +3804,25 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B103" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C103" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D103" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E103" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F103" t="s">
         <v>13</v>
       </c>
       <c r="G103" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="H103" t="s">
         <v>13</v>
@@ -3824,25 +3830,25 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B104" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C104" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D104" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E104" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F104" t="s">
         <v>13</v>
       </c>
       <c r="G104" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="H104" t="s">
         <v>13</v>
@@ -3850,25 +3856,25 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B105" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C105" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D105" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E105" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="F105" t="s">
         <v>13</v>
       </c>
       <c r="G105" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H105" t="s">
         <v>13</v>
@@ -3876,25 +3882,25 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B106" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C106" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D106" t="s">
-        <v>240</v>
+        <v>56</v>
       </c>
       <c r="E106" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="F106" t="s">
         <v>13</v>
       </c>
       <c r="G106" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="H106" t="s">
         <v>13</v>
@@ -3902,25 +3908,25 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B107" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C107" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="D107" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="E107" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="F107" t="s">
         <v>13</v>
       </c>
       <c r="G107" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="H107" t="s">
         <v>13</v>
@@ -3928,25 +3934,25 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B108" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C108" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D108" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E108" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="F108" t="s">
         <v>13</v>
       </c>
       <c r="G108" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="H108" t="s">
         <v>13</v>
@@ -3954,25 +3960,25 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B109" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C109" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D109" t="s">
         <v>68</v>
       </c>
       <c r="E109" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G109" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="H109" t="s">
         <v>13</v>
@@ -3980,25 +3986,25 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>253</v>
+      </c>
+      <c r="B110" t="s">
+        <v>245</v>
+      </c>
+      <c r="C110" t="s">
         <v>249</v>
-      </c>
-      <c r="B110" t="s">
-        <v>243</v>
-      </c>
-      <c r="C110" t="s">
-        <v>247</v>
       </c>
       <c r="D110" t="s">
         <v>68</v>
       </c>
       <c r="E110" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F110" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="G110" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H110" t="s">
         <v>13</v>
@@ -4006,25 +4012,25 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C111" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D111" t="s">
         <v>68</v>
       </c>
       <c r="E111" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="F111" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="G111" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H111" t="s">
         <v>13</v>
@@ -4032,25 +4038,25 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B112" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C112" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E112" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F112" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G112" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="H112" t="s">
         <v>13</v>
@@ -4058,79 +4064,27 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B113" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C113" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D113" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E113" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="F113" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="G113" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H113" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>256</v>
-      </c>
-      <c r="B114" t="s">
-        <v>243</v>
-      </c>
-      <c r="C114" t="s">
-        <v>257</v>
-      </c>
-      <c r="D114" t="s">
-        <v>56</v>
-      </c>
-      <c r="E114" t="s">
-        <v>79</v>
-      </c>
-      <c r="F114" t="s">
-        <v>79</v>
-      </c>
-      <c r="G114" t="s">
-        <v>258</v>
-      </c>
-      <c r="H114" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>256</v>
-      </c>
-      <c r="B115" t="s">
-        <v>243</v>
-      </c>
-      <c r="C115" t="s">
-        <v>257</v>
-      </c>
-      <c r="D115" t="s">
-        <v>56</v>
-      </c>
-      <c r="E115" t="s">
-        <v>101</v>
-      </c>
-      <c r="F115" t="s">
-        <v>13</v>
-      </c>
-      <c r="G115" t="s">
-        <v>258</v>
-      </c>
-      <c r="H115" t="s">
         <v>13</v>
       </c>
     </row>

--- a/app/data/label_overrides.xlsx
+++ b/app/data/label_overrides.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
   <si>
     <t xml:space="preserve">table_id</t>
   </si>
@@ -173,6 +173,237 @@
     <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship (monthly ranking), Province/Territory of Claim and Claim Month/Year</t>
   </si>
   <si>
+    <t xml:space="preserve">express_entry_ita/0dfa3675__canada_express_entry_candidates_by_province_territory_invita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Express Entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Express Entry Candidates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invited candidates who applied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category and Level of Foreign Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Level of Foreign Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level of Foreign Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/10646bd8__canada_express_entry_candidates_by_province_territory_invita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category and First Official Language Tested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Tested for First Official Language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tested for First Official Language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/59ae1445__canada_express_entry_candidates_by_province_territory_invita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category and Age Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Age Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/9741609d__canada_express_entry_candidates_by_province_territory_invita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category and Level of Canadian Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Level of Canadian Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level of Canadian Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/9f12b295__canada_express_entry_candidates_by_province_territory_invita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Census Metropolitan Area of Intended Destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/a7ee3178__canada_express_entry_candidates_by_province_territory_and_in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory and Invitation Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/d045b65d__canada_express_entry_candidates_by_province_territory_invita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category and Field of Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Field of Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field of Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/e8376ee8__canada_express_entry_candidates_by_province_territory_invita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category and CRS Score at Invitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Invitation to Apply (ITA) Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation to Apply (ITA) Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRS Score at Invitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/c31d6d64__canada_express_entry_candidates_by_province_territory_invita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Express Entry Candidates 2025 ranking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category and Country of Citizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Country of Citizenship (2025 ranking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/bdc973c2__canada_express_entry_candidates_under_canadian_experience_cl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Express Entry Candidates under Canadian Experience Class Invitation Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invited candidates who applied (Canadian Experience Class)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates under Canadian Experience Class Invitation Category by Province/Territory and Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/e3b94297__canada_express_entry_candidates_under_federal_skilled_trades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Express Entry Candidates under Federal Skilled Trades Invitation Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invited candidates who applied (Federal Skilled Trades Program)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates under Federal Skilled Trades Invitation Category by Province/Territory and Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/1e1ec60e__canada_express_entry_candidates_under_federal_skilled_worker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Express Entry Candidates under Federal Skilled Worker Invitation Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invited candidates who applied (Federal Skilled Worker Program)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates under Federal Skilled Worker Invitation Category by Province/Territory and Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_ita/aecb408a__canada_express_entry_candidates_under_provincial_nominee_pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Express Entry Candidates under Provincial Nominee Program Invitation Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invited candidates who applied (Provincial Nominee Program)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates under Provincial Nominee Program Invitation Category by Province/Territory and Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_pr/287b23d1__canada_permanent_residents_under_express_entry_by_province_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permanent Residents under Express Entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admissions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Province/Territory and Country of Citizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_pr/2bf5346f__canada_permanent_residents_under_express_entry_by_province_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intended Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Province/Territory and Intended Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_pr/69595431__canada_permanent_residents_under_express_entry_by_intended_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intended Destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Census Division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Intended Destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category Level 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Census Subdivision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_pr/78bc86bc__canada_permanent_residents_under_express_entry_by_province_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Province/Territory and Age Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_pr/7b23c676__canada_permanent_residents_under_express_entry_by_gender_and</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Gender and Province/Territory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_pr/88e63879__canada_permanent_residents_under_express_entry_by_province_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immigration Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Province/Territory and Immigration Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express_entry_pr/9a2dee6b__canada_permanent_residents_under_express_entry_by_province_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country of Birth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Province/Territory and Country of Birth</t>
+  </si>
+  <si>
     <t xml:space="preserve">temporary_workers/3989b766__canada_all_international_mobility_program_imp_work_permit_ho</t>
   </si>
   <si>
@@ -365,9 +596,6 @@
     <t xml:space="preserve">Francophone admissions outside Québec</t>
   </si>
   <si>
-    <t xml:space="preserve">Immigration Category</t>
-  </si>
-  <si>
     <t xml:space="preserve">Canada ex-QC - Admissions of French-Speaking Permanent Residents within Canada (excluding Quebec) by Province/Territory of Intended Destination and Immigration Category</t>
   </si>
   <si>
@@ -401,9 +629,6 @@
     <t xml:space="preserve">Canada - Adoptions via Permanent Residence (FC6, FC9) by Country of Birth and Gender</t>
   </si>
   <si>
-    <t xml:space="preserve">Country of Birth</t>
-  </si>
-  <si>
     <t xml:space="preserve">permanent_residents/2d5c04fe__quebec_english_speaking_permanent_residents_by_immigration_c</t>
   </si>
   <si>
@@ -428,18 +653,12 @@
     <t xml:space="preserve">permanent_residents/f72b7082__canada_ex_qc_french_speaking_permanent_residents_by_immigrat</t>
   </si>
   <si>
-    <t xml:space="preserve">Category Level 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Immigration Category and Express Entry</t>
   </si>
   <si>
     <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Immigration Category</t>
   </si>
   <si>
-    <t xml:space="preserve">Express Entry</t>
-  </si>
-  <si>
     <t xml:space="preserve">permanent_residents/d839c522__canada_ex_qc_french_speaking_permanent_residents_by_province__pr_immcat</t>
   </si>
   <si>
@@ -468,9 +687,6 @@
   </si>
   <si>
     <t xml:space="preserve">French-Speaking Permanent Residents — Pr Pt Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age Group</t>
   </si>
   <si>
     <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Province/Territory and Age Group</t>
@@ -842,8 +1058,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:H113" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H113"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:H141" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H141"/>
   <tableColumns count="8">
     <tableColumn id="1" name="table_id"/>
     <tableColumn id="2" name="Theme"/>
@@ -1606,13 +1822,13 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
@@ -1620,25 +1836,25 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
         <v>54</v>
       </c>
       <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
         <v>59</v>
-      </c>
-      <c r="D19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" t="s">
-        <v>61</v>
       </c>
       <c r="H19" t="s">
         <v>13</v>
@@ -1646,25 +1862,25 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
         <v>54</v>
       </c>
       <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" t="s">
         <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" t="s">
-        <v>65</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
@@ -1672,25 +1888,25 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
         <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
@@ -1698,25 +1914,25 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
         <v>54</v>
       </c>
       <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" t="s">
         <v>67</v>
-      </c>
-      <c r="D22" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" t="s">
-        <v>72</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
@@ -1724,25 +1940,25 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
         <v>54</v>
       </c>
       <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
         <v>67</v>
-      </c>
-      <c r="D23" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" t="s">
-        <v>74</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
@@ -1750,25 +1966,25 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
         <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
@@ -1776,25 +1992,25 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
         <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
@@ -1802,25 +2018,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
         <v>54</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
@@ -1828,25 +2044,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B27" t="s">
         <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
@@ -1854,25 +2070,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
         <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E28" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s">
         <v>13</v>
@@ -1880,25 +2096,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
         <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
@@ -1906,25 +2122,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
         <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="E30" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
@@ -1932,25 +2148,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E31" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F31" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G31" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
@@ -1958,25 +2174,25 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
         <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
@@ -1984,25 +2200,25 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D33" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E33" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
@@ -2010,19 +2226,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
       </c>
       <c r="C34" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" t="s">
+        <v>92</v>
+      </c>
+      <c r="E34" t="s">
         <v>93</v>
-      </c>
-      <c r="D34" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" t="s">
-        <v>97</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -2036,25 +2252,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F35" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
@@ -2062,25 +2278,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="E36" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
@@ -2088,25 +2304,25 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="E37" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F37" t="s">
         <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
@@ -2114,25 +2330,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B38" t="s">
         <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G38" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
@@ -2140,25 +2356,25 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="F39" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H39" t="s">
         <v>13</v>
@@ -2166,25 +2382,25 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E40" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="G40" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
@@ -2192,77 +2408,77 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
       </c>
       <c r="C41" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" t="s">
         <v>109</v>
       </c>
-      <c r="D41" t="s">
-        <v>104</v>
-      </c>
       <c r="E41" t="s">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="F41" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G41" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H41" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E42" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="F42" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H42" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D43" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E43" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="F43" t="s">
         <v>13</v>
       </c>
       <c r="G43" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
@@ -2270,25 +2486,25 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D44" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E44" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F44" t="s">
         <v>13</v>
       </c>
       <c r="G44" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H44" t="s">
         <v>13</v>
@@ -2296,25 +2512,25 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D45" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E45" t="s">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="F45" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="G45" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
@@ -2322,25 +2538,25 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B46" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D46" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="E46" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F46" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G46" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
@@ -2348,25 +2564,25 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B47" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C47" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E47" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G47" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H47" t="s">
         <v>13</v>
@@ -2374,25 +2590,25 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C48" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D48" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E48" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H48" t="s">
         <v>13</v>
@@ -2400,25 +2616,25 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C49" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D49" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="F49" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="G49" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="H49" t="s">
         <v>13</v>
@@ -2426,16 +2642,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="B50" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C50" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D50" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E50" t="s">
         <v>40</v>
@@ -2444,7 +2660,7 @@
         <v>13</v>
       </c>
       <c r="G50" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
@@ -2452,25 +2668,25 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C51" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D51" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E51" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="H51" t="s">
         <v>13</v>
@@ -2478,25 +2694,25 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B52" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C52" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D52" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="F52" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G52" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="H52" t="s">
         <v>13</v>
@@ -2504,51 +2720,51 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B53" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C53" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D53" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E53" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="F53" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="G53" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="H53" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B54" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C54" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D54" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="F54" t="s">
         <v>13</v>
       </c>
       <c r="G54" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="H54" t="s">
         <v>13</v>
@@ -2556,77 +2772,77 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>153</v>
+      </c>
+      <c r="B55" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" t="s">
+        <v>154</v>
+      </c>
+      <c r="D55" t="s">
         <v>145</v>
       </c>
-      <c r="B55" t="s">
-        <v>114</v>
-      </c>
-      <c r="C55" t="s">
-        <v>146</v>
-      </c>
-      <c r="D55" t="s">
-        <v>116</v>
-      </c>
       <c r="E55" t="s">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="F55" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="G55" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H55" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B56" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C56" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D56" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E56" t="s">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G56" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H56" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D57" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="E57" t="s">
-        <v>152</v>
+        <v>13</v>
       </c>
       <c r="F57" t="s">
         <v>13</v>
       </c>
       <c r="G57" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="H57" t="s">
         <v>13</v>
@@ -2634,51 +2850,51 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B58" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C58" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D58" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="E58" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="F58" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="G58" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="H58" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B59" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="D59" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E59" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="G59" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="H59" t="s">
         <v>13</v>
@@ -2686,25 +2902,25 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B60" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C60" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="D60" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E60" t="s">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="F60" t="s">
         <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="H60" t="s">
         <v>13</v>
@@ -2712,25 +2928,25 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B61" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C61" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D61" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="E61" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="F61" t="s">
         <v>13</v>
       </c>
       <c r="G61" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="H61" t="s">
         <v>13</v>
@@ -2738,25 +2954,25 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B62" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C62" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D62" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E62" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="F62" t="s">
         <v>13</v>
       </c>
       <c r="G62" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
@@ -2764,25 +2980,25 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="B63" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D63" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E63" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="G63" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="H63" t="s">
         <v>13</v>
@@ -2790,25 +3006,25 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C64" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="D64" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="E64" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="F64" t="s">
         <v>13</v>
       </c>
       <c r="G64" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="H64" t="s">
         <v>13</v>
@@ -2816,51 +3032,51 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C65" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="D65" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="G65" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="H65" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C66" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="D66" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="E66" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="F66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G66" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="H66" t="s">
         <v>13</v>
@@ -2868,25 +3084,25 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="B67" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C67" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="D67" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="E67" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G67" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="H67" t="s">
         <v>13</v>
@@ -2894,103 +3110,103 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="B68" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C68" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="D68" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="E68" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F68" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="G68" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="H68" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B69" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C69" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="D69" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="E69" t="s">
-        <v>152</v>
+        <v>13</v>
       </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="G69" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="H69" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B70" t="s">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="C70" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="D70" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="E70" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="F70" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G70" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="H70" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B71" t="s">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="C71" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="D71" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="E71" t="s">
-        <v>101</v>
+        <v>195</v>
       </c>
       <c r="F71" t="s">
         <v>13</v>
       </c>
       <c r="G71" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="H71" t="s">
         <v>13</v>
@@ -2998,25 +3214,25 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B72" t="s">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="C72" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="D72" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="E72" t="s">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="F72" t="s">
         <v>13</v>
       </c>
       <c r="G72" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="H72" t="s">
         <v>13</v>
@@ -3024,25 +3240,25 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="B73" t="s">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="C73" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="D73" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="E73" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="G73" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="H73" t="s">
         <v>13</v>
@@ -3050,25 +3266,25 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="B74" t="s">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="C74" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="D74" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="E74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F74" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="H74" t="s">
         <v>13</v>
@@ -3076,16 +3292,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="B75" t="s">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="C75" t="s">
-        <v>114</v>
+        <v>202</v>
       </c>
       <c r="D75" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="E75" t="s">
         <v>12</v>
@@ -3094,7 +3310,7 @@
         <v>12</v>
       </c>
       <c r="G75" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="H75" t="s">
         <v>13</v>
@@ -3102,51 +3318,51 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="B76" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C76" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D76" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E76" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="F76" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="G76" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="H76" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="B77" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C77" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="D77" t="s">
-        <v>13</v>
+        <v>207</v>
       </c>
       <c r="E77" t="s">
-        <v>186</v>
+        <v>125</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="G77" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="H77" t="s">
         <v>13</v>
@@ -3154,25 +3370,25 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="B78" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C78" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="D78" t="s">
-        <v>13</v>
+        <v>193</v>
       </c>
       <c r="E78" t="s">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="F78" t="s">
         <v>13</v>
       </c>
       <c r="G78" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="H78" t="s">
         <v>13</v>
@@ -3180,51 +3396,51 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="B79" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C79" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D79" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E79" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="F79" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="G79" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="H79" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>212</v>
+      </c>
+      <c r="B80" t="s">
         <v>191</v>
       </c>
-      <c r="B80" t="s">
-        <v>192</v>
-      </c>
       <c r="C80" t="s">
+        <v>210</v>
+      </c>
+      <c r="D80" t="s">
         <v>193</v>
       </c>
-      <c r="D80" t="s">
-        <v>194</v>
-      </c>
       <c r="E80" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="F80" t="s">
-        <v>196</v>
+        <v>54</v>
       </c>
       <c r="G80" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H80" t="s">
         <v>13</v>
@@ -3232,51 +3448,51 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>215</v>
+      </c>
+      <c r="B81" t="s">
         <v>191</v>
       </c>
-      <c r="B81" t="s">
-        <v>192</v>
-      </c>
       <c r="C81" t="s">
+        <v>216</v>
+      </c>
+      <c r="D81" t="s">
         <v>193</v>
       </c>
-      <c r="D81" t="s">
-        <v>194</v>
-      </c>
       <c r="E81" t="s">
-        <v>196</v>
+        <v>125</v>
       </c>
       <c r="F81" t="s">
-        <v>195</v>
+        <v>125</v>
       </c>
       <c r="G81" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="H81" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C82" t="s">
+        <v>216</v>
+      </c>
+      <c r="D82" t="s">
         <v>193</v>
       </c>
-      <c r="D82" t="s">
-        <v>194</v>
-      </c>
       <c r="E82" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="F82" t="s">
-        <v>199</v>
+        <v>13</v>
       </c>
       <c r="G82" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="H82" t="s">
         <v>13</v>
@@ -3284,77 +3500,77 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B83" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C83" t="s">
+        <v>219</v>
+      </c>
+      <c r="D83" t="s">
         <v>193</v>
       </c>
-      <c r="D83" t="s">
-        <v>194</v>
-      </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>13</v>
       </c>
       <c r="F83" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="G83" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="H83" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="B84" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C84" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="D84" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E84" t="s">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="F84" t="s">
-        <v>204</v>
+        <v>12</v>
       </c>
       <c r="G84" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="H84" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="B85" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C85" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="D85" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E85" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="F85" t="s">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="G85" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="H85" t="s">
         <v>13</v>
@@ -3362,51 +3578,51 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="B86" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C86" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="D86" t="s">
-        <v>68</v>
+        <v>193</v>
       </c>
       <c r="E86" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="F86" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="G86" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="H86" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B87" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C87" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="D87" t="s">
-        <v>68</v>
+        <v>193</v>
       </c>
       <c r="E87" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="F87" t="s">
         <v>13</v>
       </c>
       <c r="G87" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="H87" t="s">
         <v>13</v>
@@ -3414,25 +3630,25 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B88" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C88" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="D88" t="s">
-        <v>68</v>
+        <v>193</v>
       </c>
       <c r="E88" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="F88" t="s">
         <v>13</v>
       </c>
       <c r="G88" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H88" t="s">
         <v>13</v>
@@ -3440,25 +3656,25 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="B89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C89" t="s">
+        <v>229</v>
+      </c>
+      <c r="D89" t="s">
         <v>207</v>
       </c>
-      <c r="D89" t="s">
-        <v>56</v>
-      </c>
       <c r="E89" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="F89" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="G89" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="H89" t="s">
         <v>13</v>
@@ -3466,25 +3682,25 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="B90" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C90" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>193</v>
       </c>
       <c r="E90" t="s">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="F90" t="s">
         <v>13</v>
       </c>
       <c r="G90" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="H90" t="s">
         <v>13</v>
@@ -3492,25 +3708,25 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B91" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C91" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>193</v>
       </c>
       <c r="E91" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="F91" t="s">
         <v>13</v>
       </c>
       <c r="G91" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="H91" t="s">
         <v>13</v>
@@ -3518,25 +3734,25 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B92" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C92" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="D92" t="s">
-        <v>56</v>
+        <v>235</v>
       </c>
       <c r="E92" t="s">
-        <v>212</v>
+        <v>40</v>
       </c>
       <c r="F92" t="s">
         <v>13</v>
       </c>
       <c r="G92" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="H92" t="s">
         <v>13</v>
@@ -3544,51 +3760,51 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C93" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>235</v>
       </c>
       <c r="E93" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="F93" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="G93" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="H93" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B94" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C94" t="s">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="D94" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E94" t="s">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="F94" t="s">
         <v>13</v>
       </c>
       <c r="G94" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H94" t="s">
         <v>13</v>
@@ -3596,25 +3812,25 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B95" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C95" t="s">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="D95" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E95" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="F95" t="s">
         <v>13</v>
       </c>
       <c r="G95" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H95" t="s">
         <v>13</v>
@@ -3622,51 +3838,51 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B96" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C96" t="s">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="D96" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E96" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="F96" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="G96" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="H96" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B97" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C97" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="D97" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E97" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="F97" t="s">
         <v>13</v>
       </c>
       <c r="G97" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H97" t="s">
         <v>13</v>
@@ -3674,51 +3890,51 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B98" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C98" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="D98" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E98" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="G98" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H98" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B99" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C99" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="D99" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E99" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="F99" t="s">
         <v>13</v>
       </c>
       <c r="G99" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H99" t="s">
         <v>13</v>
@@ -3726,25 +3942,25 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B100" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C100" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="D100" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E100" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
       </c>
       <c r="G100" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H100" t="s">
         <v>13</v>
@@ -3752,25 +3968,25 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B101" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C101" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="D101" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E101" t="s">
-        <v>101</v>
+        <v>244</v>
       </c>
       <c r="F101" t="s">
         <v>13</v>
       </c>
       <c r="G101" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="H101" t="s">
         <v>13</v>
@@ -3778,25 +3994,25 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B102" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C102" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="D102" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E102" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="F102" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="G102" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="H102" t="s">
         <v>13</v>
@@ -3804,25 +4020,25 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B103" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="C103" t="s">
-        <v>241</v>
+        <v>191</v>
       </c>
       <c r="D103" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E103" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G103" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="H103" t="s">
         <v>13</v>
@@ -3830,51 +4046,51 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B104" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C104" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D104" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="E104" t="s">
-        <v>101</v>
+        <v>254</v>
       </c>
       <c r="F104" t="s">
-        <v>13</v>
+        <v>254</v>
       </c>
       <c r="G104" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="H104" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B105" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C105" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="D105" t="s">
-        <v>242</v>
+        <v>13</v>
       </c>
       <c r="E105" t="s">
-        <v>96</v>
+        <v>258</v>
       </c>
       <c r="F105" t="s">
         <v>13</v>
       </c>
       <c r="G105" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="H105" t="s">
         <v>13</v>
@@ -3882,25 +4098,25 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B106" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C106" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D106" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="E106" t="s">
-        <v>40</v>
+        <v>254</v>
       </c>
       <c r="F106" t="s">
         <v>13</v>
       </c>
       <c r="G106" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="H106" t="s">
         <v>13</v>
@@ -3908,51 +4124,51 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B107" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C107" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>68</v>
+        <v>254</v>
       </c>
       <c r="E107" t="s">
-        <v>40</v>
+        <v>254</v>
       </c>
       <c r="F107" t="s">
-        <v>13</v>
+        <v>254</v>
       </c>
       <c r="G107" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="H107" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B108" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C108" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="D108" t="s">
-        <v>68</v>
+        <v>266</v>
       </c>
       <c r="E108" t="s">
-        <v>69</v>
+        <v>267</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>268</v>
       </c>
       <c r="G108" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="H108" t="s">
         <v>13</v>
@@ -3960,25 +4176,25 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B109" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C109" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="D109" t="s">
-        <v>68</v>
+        <v>266</v>
       </c>
       <c r="E109" t="s">
-        <v>12</v>
+        <v>268</v>
       </c>
       <c r="F109" t="s">
-        <v>12</v>
+        <v>267</v>
       </c>
       <c r="G109" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="H109" t="s">
         <v>13</v>
@@ -3986,25 +4202,25 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="B110" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C110" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="D110" t="s">
-        <v>68</v>
+        <v>266</v>
       </c>
       <c r="E110" t="s">
-        <v>75</v>
+        <v>267</v>
       </c>
       <c r="F110" t="s">
-        <v>75</v>
+        <v>271</v>
       </c>
       <c r="G110" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="H110" t="s">
         <v>13</v>
@@ -4012,25 +4228,25 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="B111" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C111" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D111" t="s">
-        <v>68</v>
+        <v>266</v>
       </c>
       <c r="E111" t="s">
-        <v>79</v>
+        <v>271</v>
       </c>
       <c r="F111" t="s">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="G111" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="H111" t="s">
         <v>13</v>
@@ -4038,25 +4254,25 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="B112" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D112" t="s">
-        <v>56</v>
+        <v>266</v>
       </c>
       <c r="E112" t="s">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="F112" t="s">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="G112" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="H112" t="s">
         <v>13</v>
@@ -4064,27 +4280,755 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="B113" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D113" t="s">
-        <v>56</v>
+        <v>266</v>
       </c>
       <c r="E113" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="F113" t="s">
-        <v>13</v>
+        <v>275</v>
       </c>
       <c r="G113" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="H113" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>278</v>
+      </c>
+      <c r="B114" t="s">
+        <v>264</v>
+      </c>
+      <c r="C114" t="s">
+        <v>279</v>
+      </c>
+      <c r="D114" t="s">
+        <v>145</v>
+      </c>
+      <c r="E114" t="s">
+        <v>12</v>
+      </c>
+      <c r="F114" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" t="s">
+        <v>280</v>
+      </c>
+      <c r="H114" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>281</v>
+      </c>
+      <c r="B115" t="s">
+        <v>264</v>
+      </c>
+      <c r="C115" t="s">
+        <v>279</v>
+      </c>
+      <c r="D115" t="s">
+        <v>145</v>
+      </c>
+      <c r="E115" t="s">
+        <v>40</v>
+      </c>
+      <c r="F115" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" t="s">
+        <v>282</v>
+      </c>
+      <c r="H115" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>283</v>
+      </c>
+      <c r="B116" t="s">
+        <v>264</v>
+      </c>
+      <c r="C116" t="s">
+        <v>279</v>
+      </c>
+      <c r="D116" t="s">
+        <v>145</v>
+      </c>
+      <c r="E116" t="s">
+        <v>284</v>
+      </c>
+      <c r="F116" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" t="s">
+        <v>285</v>
+      </c>
+      <c r="H116" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>286</v>
+      </c>
+      <c r="B117" t="s">
+        <v>264</v>
+      </c>
+      <c r="C117" t="s">
+        <v>279</v>
+      </c>
+      <c r="D117" t="s">
+        <v>133</v>
+      </c>
+      <c r="E117" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" t="s">
+        <v>187</v>
+      </c>
+      <c r="G117" t="s">
+        <v>287</v>
+      </c>
+      <c r="H117" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>288</v>
+      </c>
+      <c r="B118" t="s">
+        <v>264</v>
+      </c>
+      <c r="C118" t="s">
+        <v>289</v>
+      </c>
+      <c r="D118" t="s">
+        <v>133</v>
+      </c>
+      <c r="E118" t="s">
+        <v>284</v>
+      </c>
+      <c r="F118" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" t="s">
+        <v>290</v>
+      </c>
+      <c r="H118" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>291</v>
+      </c>
+      <c r="B119" t="s">
+        <v>264</v>
+      </c>
+      <c r="C119" t="s">
+        <v>292</v>
+      </c>
+      <c r="D119" t="s">
+        <v>133</v>
+      </c>
+      <c r="E119" t="s">
+        <v>40</v>
+      </c>
+      <c r="F119" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" t="s">
+        <v>293</v>
+      </c>
+      <c r="H119" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>294</v>
+      </c>
+      <c r="B120" t="s">
+        <v>264</v>
+      </c>
+      <c r="C120" t="s">
+        <v>292</v>
+      </c>
+      <c r="D120" t="s">
+        <v>133</v>
+      </c>
+      <c r="E120" t="s">
+        <v>284</v>
+      </c>
+      <c r="F120" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" t="s">
+        <v>295</v>
+      </c>
+      <c r="H120" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>296</v>
+      </c>
+      <c r="B121" t="s">
+        <v>264</v>
+      </c>
+      <c r="C121" t="s">
+        <v>297</v>
+      </c>
+      <c r="D121" t="s">
+        <v>133</v>
+      </c>
+      <c r="E121" t="s">
+        <v>40</v>
+      </c>
+      <c r="F121" t="s">
+        <v>13</v>
+      </c>
+      <c r="G121" t="s">
+        <v>298</v>
+      </c>
+      <c r="H121" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>299</v>
+      </c>
+      <c r="B122" t="s">
+        <v>300</v>
+      </c>
+      <c r="C122" t="s">
+        <v>301</v>
+      </c>
+      <c r="D122" t="s">
+        <v>302</v>
+      </c>
+      <c r="E122" t="s">
+        <v>125</v>
+      </c>
+      <c r="F122" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" t="s">
+        <v>303</v>
+      </c>
+      <c r="H122" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>299</v>
+      </c>
+      <c r="B123" t="s">
+        <v>300</v>
+      </c>
+      <c r="C123" t="s">
+        <v>301</v>
+      </c>
+      <c r="D123" t="s">
+        <v>302</v>
+      </c>
+      <c r="E123" t="s">
+        <v>178</v>
+      </c>
+      <c r="F123" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" t="s">
+        <v>303</v>
+      </c>
+      <c r="H123" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>299</v>
+      </c>
+      <c r="B124" t="s">
+        <v>300</v>
+      </c>
+      <c r="C124" t="s">
+        <v>301</v>
+      </c>
+      <c r="D124" t="s">
+        <v>302</v>
+      </c>
+      <c r="E124" t="s">
+        <v>173</v>
+      </c>
+      <c r="F124" t="s">
+        <v>13</v>
+      </c>
+      <c r="G124" t="s">
+        <v>303</v>
+      </c>
+      <c r="H124" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>304</v>
+      </c>
+      <c r="B125" t="s">
+        <v>300</v>
+      </c>
+      <c r="C125" t="s">
+        <v>305</v>
+      </c>
+      <c r="D125" t="s">
+        <v>306</v>
+      </c>
+      <c r="E125" t="s">
+        <v>125</v>
+      </c>
+      <c r="F125" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" t="s">
+        <v>307</v>
+      </c>
+      <c r="H125" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>304</v>
+      </c>
+      <c r="B126" t="s">
+        <v>300</v>
+      </c>
+      <c r="C126" t="s">
+        <v>305</v>
+      </c>
+      <c r="D126" t="s">
+        <v>306</v>
+      </c>
+      <c r="E126" t="s">
+        <v>178</v>
+      </c>
+      <c r="F126" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" t="s">
+        <v>307</v>
+      </c>
+      <c r="H126" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>304</v>
+      </c>
+      <c r="B127" t="s">
+        <v>300</v>
+      </c>
+      <c r="C127" t="s">
+        <v>305</v>
+      </c>
+      <c r="D127" t="s">
+        <v>306</v>
+      </c>
+      <c r="E127" t="s">
+        <v>173</v>
+      </c>
+      <c r="F127" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" t="s">
+        <v>307</v>
+      </c>
+      <c r="H127" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>308</v>
+      </c>
+      <c r="B128" t="s">
+        <v>300</v>
+      </c>
+      <c r="C128" t="s">
+        <v>309</v>
+      </c>
+      <c r="D128" t="s">
+        <v>310</v>
+      </c>
+      <c r="E128" t="s">
+        <v>125</v>
+      </c>
+      <c r="F128" t="s">
+        <v>13</v>
+      </c>
+      <c r="G128" t="s">
+        <v>311</v>
+      </c>
+      <c r="H128" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>308</v>
+      </c>
+      <c r="B129" t="s">
+        <v>300</v>
+      </c>
+      <c r="C129" t="s">
+        <v>309</v>
+      </c>
+      <c r="D129" t="s">
+        <v>310</v>
+      </c>
+      <c r="E129" t="s">
+        <v>178</v>
+      </c>
+      <c r="F129" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129" t="s">
+        <v>311</v>
+      </c>
+      <c r="H129" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>308</v>
+      </c>
+      <c r="B130" t="s">
+        <v>300</v>
+      </c>
+      <c r="C130" t="s">
+        <v>309</v>
+      </c>
+      <c r="D130" t="s">
+        <v>310</v>
+      </c>
+      <c r="E130" t="s">
+        <v>173</v>
+      </c>
+      <c r="F130" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" t="s">
+        <v>311</v>
+      </c>
+      <c r="H130" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>312</v>
+      </c>
+      <c r="B131" t="s">
+        <v>300</v>
+      </c>
+      <c r="C131" t="s">
+        <v>313</v>
+      </c>
+      <c r="D131" t="s">
+        <v>314</v>
+      </c>
+      <c r="E131" t="s">
+        <v>125</v>
+      </c>
+      <c r="F131" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" t="s">
+        <v>315</v>
+      </c>
+      <c r="H131" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>312</v>
+      </c>
+      <c r="B132" t="s">
+        <v>300</v>
+      </c>
+      <c r="C132" t="s">
+        <v>313</v>
+      </c>
+      <c r="D132" t="s">
+        <v>314</v>
+      </c>
+      <c r="E132" t="s">
+        <v>178</v>
+      </c>
+      <c r="F132" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" t="s">
+        <v>315</v>
+      </c>
+      <c r="H132" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>312</v>
+      </c>
+      <c r="B133" t="s">
+        <v>300</v>
+      </c>
+      <c r="C133" t="s">
+        <v>313</v>
+      </c>
+      <c r="D133" t="s">
+        <v>314</v>
+      </c>
+      <c r="E133" t="s">
+        <v>173</v>
+      </c>
+      <c r="F133" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" t="s">
+        <v>315</v>
+      </c>
+      <c r="H133" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>316</v>
+      </c>
+      <c r="B134" t="s">
+        <v>317</v>
+      </c>
+      <c r="C134" t="s">
+        <v>318</v>
+      </c>
+      <c r="D134" t="s">
+        <v>133</v>
+      </c>
+      <c r="E134" t="s">
+        <v>40</v>
+      </c>
+      <c r="F134" t="s">
+        <v>13</v>
+      </c>
+      <c r="G134" t="s">
+        <v>319</v>
+      </c>
+      <c r="H134" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>320</v>
+      </c>
+      <c r="B135" t="s">
+        <v>317</v>
+      </c>
+      <c r="C135" t="s">
+        <v>321</v>
+      </c>
+      <c r="D135" t="s">
+        <v>145</v>
+      </c>
+      <c r="E135" t="s">
+        <v>40</v>
+      </c>
+      <c r="F135" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" t="s">
+        <v>322</v>
+      </c>
+      <c r="H135" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>323</v>
+      </c>
+      <c r="B136" t="s">
+        <v>317</v>
+      </c>
+      <c r="C136" t="s">
+        <v>321</v>
+      </c>
+      <c r="D136" t="s">
+        <v>145</v>
+      </c>
+      <c r="E136" t="s">
+        <v>146</v>
+      </c>
+      <c r="F136" t="s">
+        <v>13</v>
+      </c>
+      <c r="G136" t="s">
+        <v>324</v>
+      </c>
+      <c r="H136" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>325</v>
+      </c>
+      <c r="B137" t="s">
+        <v>317</v>
+      </c>
+      <c r="C137" t="s">
+        <v>321</v>
+      </c>
+      <c r="D137" t="s">
+        <v>145</v>
+      </c>
+      <c r="E137" t="s">
+        <v>12</v>
+      </c>
+      <c r="F137" t="s">
+        <v>12</v>
+      </c>
+      <c r="G137" t="s">
+        <v>326</v>
+      </c>
+      <c r="H137" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>325</v>
+      </c>
+      <c r="B138" t="s">
+        <v>317</v>
+      </c>
+      <c r="C138" t="s">
+        <v>321</v>
+      </c>
+      <c r="D138" t="s">
+        <v>145</v>
+      </c>
+      <c r="E138" t="s">
+        <v>152</v>
+      </c>
+      <c r="F138" t="s">
+        <v>152</v>
+      </c>
+      <c r="G138" t="s">
+        <v>326</v>
+      </c>
+      <c r="H138" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>327</v>
+      </c>
+      <c r="B139" t="s">
+        <v>317</v>
+      </c>
+      <c r="C139" t="s">
+        <v>328</v>
+      </c>
+      <c r="D139" t="s">
+        <v>145</v>
+      </c>
+      <c r="E139" t="s">
+        <v>156</v>
+      </c>
+      <c r="F139" t="s">
+        <v>156</v>
+      </c>
+      <c r="G139" t="s">
+        <v>329</v>
+      </c>
+      <c r="H139" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>330</v>
+      </c>
+      <c r="B140" t="s">
+        <v>317</v>
+      </c>
+      <c r="C140" t="s">
+        <v>331</v>
+      </c>
+      <c r="D140" t="s">
+        <v>133</v>
+      </c>
+      <c r="E140" t="s">
+        <v>156</v>
+      </c>
+      <c r="F140" t="s">
+        <v>156</v>
+      </c>
+      <c r="G140" t="s">
+        <v>332</v>
+      </c>
+      <c r="H140" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>330</v>
+      </c>
+      <c r="B141" t="s">
+        <v>317</v>
+      </c>
+      <c r="C141" t="s">
+        <v>331</v>
+      </c>
+      <c r="D141" t="s">
+        <v>133</v>
+      </c>
+      <c r="E141" t="s">
+        <v>178</v>
+      </c>
+      <c r="F141" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" t="s">
+        <v>332</v>
+      </c>
+      <c r="H141" t="s">
         <v>13</v>
       </c>
     </row>
